--- a/data/google_news_dedup_02_0426_UTC_past2d.xlsx
+++ b/data/google_news_dedup_02_0426_UTC_past2d.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,22 +490,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FedEx goes after DoorDash, Amazon, UPS with same-day delivery - Modern Retail</t>
+          <t>Postcodes in Wales hit by Royal Mail delivery disruption today — full list - walesonline.co.uk</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FedEx goes after DoorDash, Amazon, UPS with same-day delivery - Modern Retail</t>
+          <t>Postcodes in Wales hit by Royal Mail delivery disruption today — full list - walesonline.co.uk</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 04:03:25 GMT</t>
+          <t>Thu, 02 Apr 2026 08:54:00 GMT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNeXozaDUwb0E2ZjJWQkp4YTNRc052VDFBWWJiT0xIZGpGQnFCTG91S0RyRjd6R3J4a0MwTDFJMWtBamM0SWFyQUkwRGtxSzhETHdubGdSUkhUbkthQVg5S3JJTXhGcGJRVlRHX3N4UGREQ3pJNVFSTy1CSTFHU3FTZmhSQzFlU3dqM1JtNFJEY1FBeGFSNnp2a29jaExfMVVp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPRnoxeE1fY190NndXSjBqV3piVHhhRWR0Sy1ieXZud2RTeTFaSG1EcG1JM3dZRlk4MkFIdGZKTkxraU1KNTZBWFFXbndCblR1a0pkZHhnclY1SkdCalRvaV9iNlotaXNyNzA5cG9CX2hIUldjWkxmcWdZdTRScFFFblVIMWc4UlRDa3JJWG9R0gGTAUFVX3lxTE1jLTlJcXEyZ19YM1g5cUhyN1NPV2MxZmxyc1lwbm1HUE94QTB4bFRONXdwcmhpYlBrNFZxMUdCYVliLTJHZ1ZiUXNnRnZ6M3BJSW9LY2s3V3g1aVZpczJxWnN0RmNKeVV6S1hJX0licTZNc2lsZE5yWmY0YzJ5TkRhSXE1Wm5ORDc5clRxcnZtMEgtcw?oc=5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46114.16903935185</v>
+        <v>46114.37083333333</v>
       </c>
     </row>
     <row r="3">
@@ -600,22 +600,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>130+ of the top deals during Amazon’s Big Spring Sale 2026 you can shop now - About Amazon</t>
+          <t>FedEx goes after DoorDash, Amazon, UPS with same-day delivery - Modern Retail</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>130+ of the top deals during Amazon’s Big Spring Sale 2026 you can shop now - About Amazon</t>
+          <t>FedEx goes after DoorDash, Amazon, UPS with same-day delivery - Modern Retail</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 02:03:56 GMT</t>
+          <t>Thu, 02 Apr 2026 04:03:25 GMT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQazlkcW1kWHVfUVgzVXQtdFlNV3doaGFpTGV3UnIydldvcXdlMTF6bjFBeDNGMDMtWkVBb0JNU0hDYzBwdGFIV2FoSjNaUFhxYXNHdGRPN2NNbl8ybE9vcnJ3V1NhZThLamtKWF8wNVpwLW4tLU5MLThDUDhscjUwLW9tTkY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNeXozaDUwb0E2ZjJWQkp4YTNRc052VDFBWWJiT0xIZGpGQnFCTG91S0RyRjd6R3J4a0MwTDFJMWtBamM0SWFyQUkwRGtxSzhETHdubGdSUkhUbkthQVg5S3JJTXhGcGJRVlRHX3N4UGREQ3pJNVFSTy1CSTFHU3FTZmhSQzFlU3dqM1JtNFJEY1FBeGFSNnp2a29jaExfMVVp?oc=5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46114.08606481482</v>
+        <v>46114.16903935185</v>
       </c>
     </row>
     <row r="5">
@@ -655,22 +655,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DHL Supply Chain Expands Airport Role With Air France-KLM - Supply Chain Digital Magazine</t>
+          <t>130+ of the top deals during Amazon’s Big Spring Sale 2026 you can shop now - About Amazon</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DHL Supply Chain Expands Airport Role With Air France-KLM - Supply Chain Digital Magazine</t>
+          <t>130+ of the top deals during Amazon’s Big Spring Sale 2026 you can shop now - About Amazon</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 11:25:58 GMT</t>
+          <t>Thu, 02 Apr 2026 02:03:56 GMT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPRTRERzh1akhtTExIWFAzVlhBandsTExpeTVqelZfOVNxa1pXRGFkdS1zVkZwQWNQd3dxRk5SSUlFaWdRWGdrYVpqSXEzTks2aFRtNTliSzBKMmhyOS1iMHZoeGhLYjAtS2F2dDhmMXBucDZrejF3N3Y2YjN0WEpoaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQazlkcW1kWHVfUVgzVXQtdFlNV3doaGFpTGV3UnIydldvcXdlMTF6bjFBeDNGMDMtWkVBb0JNU0hDYzBwdGFIV2FoSjNaUFhxYXNHdGRPN2NNbl8ybE9vcnJ3V1NhZThLamtKWF8wNVpwLW4tLU5MLThDUDhscjUwLW9tTkY?oc=5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46113.47636574074</v>
+        <v>46114.08606481482</v>
       </c>
     </row>
     <row r="6">
@@ -765,22 +765,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Best Flower Delivery Services 2026: Spring Blooms To Brighten Any Space - Forbes</t>
+          <t>Inside Beaver's New Amazon Facility: Hundreds of Jobs, Same-Day Delivery, and Still Growing - WOAY-TV</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Best Flower Delivery Services 2026: Spring Blooms To Brighten Any Space - Forbes</t>
+          <t>Inside Beaver's New Amazon Facility: Hundreds of Jobs, Same-Day Delivery, and Still Growing - WOAY-TV</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 15:30:10 GMT</t>
+          <t>Wed, 01 Apr 2026 21:44:47 GMT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOLWRiU0haUnFyQ0tNVGpZMDdYWE5LeG9KOVV0dU1MY2poMlNmVFgweWdfbXJ2cUpIemk2ZU84VWRFanZ0NER3M0hnMUl4OE1oS003RTU4TXFTaGdpVTVaTXhmWFlYakpFSVF5eVVqYWtZNC00bFp6ZlpyaE1uVEhFYlBlaXNZd2xud3lrTzdRQVV3MzA1?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWnVDdWsyUkRhN3pRQlpoUTBFemRVLVEybGJVZk5CR2xpTHRVcWdCcWdLb1AtUGluZnFDY01RdE5UQmtvMVQ4cnBDRG5UNlNnb3BDUi1BSkVJTWNseEJGdFVaREJPRUxzTjhKdDNDODk3QkxIRk03b3Izd2Z1UWc1SV9Ld0F5R2xLcDQ0ZmNZR0Z0NTVOTWkzRm9nUzFJNG1fbmxVQ2VETk7SAa4BQVVfeXFMT0Iwd1V0cXZQZlNaWTQ0TWFNTDNJYndNSTdoYkx5Y20yYjFudlQ4Q2w2QUxkU3ZtR0duSjVnTllyUkNEUVpTYjQwaW92N0Z3THlkV3RhWFpuaTctbUQyQzB0T25LQkdWdjM0Z1JWVDg0NlNGV2xISV81MFh2S2VBMmFVYlZoU1pSeEljMWpBM2d3U2tfOVVfaUxCMjJxdmJKM2tkTjN4Y1pFSU1Db1pn?oc=5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46113.64594907407</v>
+        <v>46113.90609953704</v>
       </c>
     </row>
     <row r="8">
@@ -875,22 +875,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inside Beaver's New Amazon Facility: Hundreds of Jobs, Same-Day Delivery, and Still Growing - WOAY-TV</t>
+          <t>Amazon Is Making Fresh Grocery Delivery Easier — and More Affordable - amny.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Inside Beaver's New Amazon Facility: Hundreds of Jobs, Same-Day Delivery, and Still Growing - WOAY-TV</t>
+          <t>Amazon Is Making Fresh Grocery Delivery Easier — and More Affordable - amny.com</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 21:44:47 GMT</t>
+          <t>Wed, 01 Apr 2026 19:14:35 GMT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxPWnVDdWsyUkRhN3pRQlpoUTBFemRVLVEybGJVZk5CR2xpTHRVcWdCcWdLb1AtUGluZnFDY01RdE5UQmtvMVQ4cnBDRG5UNlNnb3BDUi1BSkVJTWNseEJGdFVaREJPRUxzTjhKdDNDODk3QkxIRk03b3Izd2Z1UWc1SV9Ld0F5R2xLcDQ0ZmNZR0Z0NTVOTWkzRm9nUzFJNG1fbmxVQ2VETk7SAa4BQVVfeXFMT0Iwd1V0cXZQZlNaWTQ0TWFNTDNJYndNSTdoYkx5Y20yYjFudlQ4Q2w2QUxkU3ZtR0duSjVnTllyUkNEUVpTYjQwaW92N0Z3THlkV3RhWFpuaTctbUQyQzB0T25LQkdWdjM0Z1JWVDg0NlNGV2xISV81MFh2S2VBMmFVYlZoU1pSeEljMWpBM2d3U2tfOVVfaUxCMjJxdmJKM2tkTjN4Y1pFSU1Db1pn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVzg1R2lQRXVCSzFvaDd1LVluOFhJckk4bXM0bFVObDNWVGl1dHpnaWpSTFJOLWNfQUNCUjBhQ29LTlhDM2dNTmR4cGtjeVNkLVh2YjBkcGFMYzhxRERCSkFRYnZkWDNRR28tRzRmaXJXSXE2N3V4QXVRWWRtelNFVFdPNWdaZHdXeGZYSlFiZ1puSU4wR3NuRHJ4VHIwVVE?oc=5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46113.90609953704</v>
+        <v>46113.80179398148</v>
       </c>
     </row>
     <row r="10">
@@ -930,22 +930,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>How DHL Supply Chain Preps for ‘Most Unpredictable Peak Season’ - WWD</t>
+          <t>Relief for hotels as govt ups LPG supply - The Times of India</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>How DHL Supply Chain Preps for ‘Most Unpredictable Peak Season’ - WWD</t>
+          <t>Relief for hotels as govt ups LPG supply - The Times of India</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 13:38:35 GMT</t>
+          <t>Wed, 01 Apr 2026 18:32:00 GMT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxONXJ3a0lpXzZOT1RMYXhXQTdMWk9EanRaNlZjTGEyTmxCbUVDdjhpRkFERnhLWVdrcEg5OEJXWk1Gb25oYlRkNzYwVUlyaUxyNzVFVC1kdFl5ZzFhR1hHSHlsWURJZ2ZsVWZsWDQ4d3JXZXV0V2E1YS0xV1Q5STZaX1RBMVlEbGxjU2k1eVRlMDBsMlZ0MGluc1JQbmRFbEZUZWc0QVI3cDFxVC1pN3NZWjVQQmI4N00zZ1dqclU2cWZWd2dPYnpFUnVXUDk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPLUs3T1dqTU1NYklwZTNNaEtuTnNINVJzZEVJTElJNlpQVEV5TkJRS05Md2ljV2VRQllPdmIwQmpwSnJ2VG11Tk5SOGk5cWU3VnRQNVZicTU4UzQ2ekp5eG0xMEF4ZS1TekFOZmNiUEhrWFB6RjJTekZ1XzE3M3hoY2ZabGVSdjZrVlgxUTYyekQtdE9lRHVteFRCWWtHT1VXd20tMlQxc1dteFJ4bWRLRNIBtgFBVV95cUxQQU55ejNTR2FzQnNUWHJNZnI2dlNuY3lBUjI2cGJLdldUel9uQlFFOEwwVU1zR2NEblN6MFh4X3ZRVTkzTVdOQ2dVWGE2SVpnSmdPTU5pRjU5N20wUFI5dDFoVERaWnZvb2NPUUZPQmZtbEl1d0pwVTZEVlZ3V1BMLTA4c09JRzJkSmlmdVVoOENxdmREc2pPd3J1V0FGaFAyNUJQckc2X1Y1RFBJWENsTFlaVkh5UQ?oc=5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46113.56846064814</v>
+        <v>46113.77222222222</v>
       </c>
     </row>
     <row r="11">
@@ -985,22 +985,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FedEx’s next AI leap to feature RFID, robotics - Supply Chain Dive</t>
+          <t>DHL Supply Chain Expands Airport Role With Air France-KLM - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FedEx’s next AI leap to feature RFID, robotics - Supply Chain Dive</t>
+          <t>DHL Supply Chain Expands Airport Role With Air France-KLM - Supply Chain Digital Magazine</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 14:04:51 GMT</t>
+          <t>Wed, 01 Apr 2026 11:25:58 GMT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOeThLcGpmMFBCTjRLV3dNYWliWWFHZ0lUdGtiazEyQnM4LV90QjZ0a1pMT0VMT1ZKVlF6cTNDaWh6TUZBelc4ekJHZkN6eTJuT2NDLXNvMm1ia3ROZmJ6ZHpLZFYzMEtkTnI3Q3g4anlUR1pIUUZEbVk2aWdvWmNWNWprOVJPVmtPMTdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPRTRERzh1akhtTExIWFAzVlhBandsTExpeTVqelZfOVNxa1pXRGFkdS1zVkZwQWNQd3dxRk5SSUlFaWdRWGdrYVpqSXEzTks2aFRtNTliSzBKMmhyOS1iMHZoeGhLYjAtS2F2dDhmMXBucDZrejF3N3Y2YjN0WEpoaQ?oc=5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46113.58670138889</v>
+        <v>46113.47636574074</v>
       </c>
     </row>
     <row r="12">
@@ -1040,22 +1040,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Amazon Is Making Fresh Grocery Delivery Easier — and More Affordable - amny.com</t>
+          <t>How DHL Supply Chain Preps for ‘Most Unpredictable Peak Season’ - WWD</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Amazon Is Making Fresh Grocery Delivery Easier — and More Affordable - amny.com</t>
+          <t>How DHL Supply Chain Preps for ‘Most Unpredictable Peak Season’ - WWD</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 19:14:35 GMT</t>
+          <t>Wed, 01 Apr 2026 13:38:35 GMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOVzg1R2lQRXVCSzFvaDd1LVluOFhJckk4bXM0bFVObDNWVGl1dHpnaWpSTFJOLWNfQUNCUjBhQ29LTlhDM2dNTmR4cGtjeVNkLVh2YjBkcGFMYzhxRERCSkFRYnZkWDNRR28tRzRmaXJXSXE2N3V4QXVRWWRtelNFVFdPNWdaZHdXeGZYSlFiZ1puSU4wR3NuRHJ4VHIwVVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxONXJ3a0lpXzZOT1RMYXhXQTdMWk9EanRaNlZjTGEyTmxCbUVDdjhpRkFERnhLWVdrcEg5OEJXWk1Gb25oYlRkNzYwVUlyaUxyNzVFVC1kdFl5ZzFhR1hHSHlsWURJZ2ZsVWZsWDQ4d3JXZXV0V2E1YS0xV1Q5STZaX1RBMVlEbGxjU2k1eVRlMDBsMlZ0MGluc1JQbmRFbEZUZWc0QVI3cDFxVC1pN3NZWjVQQmI4N00zZ1dqclU2cWZWd2dPYnpFUnVXUDk?oc=5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1079,38 +1079,38 @@
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46113.80179398148</v>
+        <v>46113.56846064814</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Relief for hotels as govt ups LPG supply - The Times of India</t>
+          <t>Drugsoorlog in Brussel blijft duren: teller dit jaar al op 22 schietpartijen na nieuw incident in Anderlecht - HLN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Relief for hotels as govt ups LPG supply - The Times of India</t>
+          <t>Drug war in Brussels continues: 22 shootings this year after new incident in Anderlecht - HLN</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 18:32:00 GMT</t>
+          <t>Thu, 02 Apr 2026 08:33:35 GMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPLUs3T1dqTU1NYklwZTNNaEtuTnNINVJzZEVJTElJNlpQVEV5TkJRS05Md2ljV2VRQllPdmIwQmpwSnJ2VG11Tk5SOGk5cWU3VnRQNVZicTU4UzQ2ekp5eG0xMEF4ZS1TekFOZmNiUEhrWFB6RjJTekZ1XzE3M3hoY2ZabGVSdjZrVlgxUTYyekQtdE9lRHVteFRCWWtHT1VXd20tMlQxc1dteFJ4bWRLRNIBtgFBVV95cUxQQU55ejNTR2FzQnNUWHJNZnI2dlNuY3lBUjI2cGJLdldUel9uQlFFOEwwVU1zR2NEblN6MFh4X3ZRVTkzTVdOQ2dVWGE2SVpnSmdPTU5pRjU5N20wUFI5dDFoVERaWnZvb2NPUUZPQmZtbEl1d0pwVTZEVlZ3V1BMLTA4c09JRzJkSmlmdVVoOENxdmREc2pPd3J1V0FGaFAyNUJQckc2X1Y1RFBJWENsTFlaVkh5UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOWERNaDA2NFk5R1pfTXk5WlFsNkEwUkFmQ2NXbXN4MFd2dEE1UEpIX2ZYVENnNU90Z25nZ09OUlhfd2ZKOGlxNGhXZkdXSURMc0xZNkpNUko5RkU4UnhjR3VDMFJES0YtZm5EamlzM0hnRFJOSkdZSnM0MmlpZ3lFYm1mbGpKcnlPY2dHWUZZZFdhYXdvUDV3T1Z0ZDRTd1hBTVVEbXJJWVVZaXNOUnNlbW55cXFvc1ozUUg3MVlURERLWHhMQXpwRmgwd29MZG1Rcm5hbGRIaGQzdm1R?oc=5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1120,52 +1120,52 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46113.77222222222</v>
+        <v>46114.35665509259</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EEOC sues DHL Supply Chain for denying disability accommodation, firing worker - hcamag.com</t>
+          <t>Man krijgt kogel in de arm bij schietpartij vlak bij metrostation Clemenceau in Anderlecht - VRT</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EEOC sues DHL Supply Chain for denying disability accommodation, firing worker - hcamag.com</t>
+          <t>Man gets shot in the arm during shooting near Clemenceau metro station in Anderlecht - VRT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 20:34:02 GMT</t>
+          <t>Wed, 01 Apr 2026 14:42:24 GMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQOVhLMlNZYWVmc0VYNjhtdEhfT2I5TWpPY1ZwanNfcERZdHRpM0E1Yi1NN01ZVHp2Y09sbkxWN2Q0bWxJby13OHVzMWpkVzdjakk0dnpaM1didVk0cHVsUnVzS2JoVUFyT3NoR1Rmd2s2ZmJiVWVXOXNPQ0d6RVJYVmh1VGdZc0hBOTVZdUFpZzFacE9Jb2FtNGZjQ1ZfbE5ZYUlPOTVHY1ZMZ2dKdHdmZnpPZnpodDdsdHV4TldlMXg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQVkRnNGhSV0NJN2lFZ2daX3RtY2stcU9ZbzlZaVhaT3NlcUliOU13NVowNFQzQkk3V1hYLWhfRzBBSmZBSUdlTzVDZzdoRng3aG1hUzRKdnVDbjNfbklqRlp3QjFWSU5XbnJrNXZ6dXM3cTdnNWFRRnZwaW8yQkRlRXNYZGp6UlJVY0QxQlU3NDM2aDRINVl3RDZMdFd5eEJTR3Q2OERMX1E?oc=5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1175,21 +1175,21 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46113.85696759259</v>
+        <v>46113.61277777778</v>
       </c>
     </row>
     <row r="15">
@@ -1205,22 +1205,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>“Je gaat zien, je gaat branden”: Vrouwen veroordeeld voor explosie in Deurne - GVA</t>
+          <t>“Ze is dagenlang geterroriseerd, gestalkt en belaagd door die vrouwen”: rechtbank oordeelt zwaar over dames die explosief naar voordeur van vriendin gooiden - pzc.nl</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>“You're going to see, you're going to burn”: Women convicted for explosion in Deurne - GVA</t>
+          <t>“She was terrorized, stalked and harassed by those women for days”: court judges heavily about ladies who threw explosive at girlfriend's front door - pzc.nl</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 10:47:41 GMT</t>
+          <t>Wed, 01 Apr 2026 18:32:00 GMT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQZmxiWlBGTjBrQnJtNnJMYUl1aW5adE9VaXlnOFViUkwwOWp6bHptS3FtQlVkMkVzTnR5YnZRbkQtOFRmbU9kXzZNV3psSUV0cjZNSk9aOVZEVGZzOXhMYzJDeUtXWGlabzBwQTFjajNQZVZJaG9wUHhHQXJ4WXk2VF9nRHB1OV9zUmJpTGtnakY4WU4wYzI1TXNQMjh3YVZRREZGU0lKa3FhMDMzQzdqN1lCRDJsdkdzazdxZEpVQS1VSTB1Y05TOXF2UW81TWRzR05rTWNDajVWZkR5N1lzeFhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxPNmdLQ1dmOU12dHg5bWxRbWxrWmZOb3AtckVaRnNzejZtOHlETEhmXzI0N0duNzloNlZxd2N0X2F5Q05NaHlydnhBdDAxcjVfT3g0LW5ESlo4RXdTSWoxQlR2UkNVZUZfRFU5R3ZhWE9VRjRFU09vNE1faUs1cXFUZi16M09id2NZZDBVVEY5bFBvblFaNDNENUE1QkZiS1FkNGl0SGhUMGwtYXpITlZLaDl6QzNNelh1Zmc3RHFoRXUyeTdGbGhzSWtmM3BVSVpHVFZtMmZVa0xaR0FSZWJvTFlZX3k1Z2FIbWVPNWpkdms3RUpWcUswU05nZ0tDQU5EeVdrZ09RU0RnVnZOMVA3b0VQMkU1LVdXc3VV?oc=5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46113.44978009259</v>
+        <v>46113.77222222222</v>
       </c>
     </row>
     <row r="16">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Schietpartij Anderlecht: slachtoffer kreeg kogel in arm - Nieuwsblad</t>
+          <t>“Je gaat zien, je gaat branden”: Vrouwen veroordeeld voor explosie in Deurne - GVA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Anderlecht shooting: victim was shot in the arm - Nieuwsblad</t>
+          <t>“You're going to see, you're going to burn”: Women convicted for explosion in Deurne - GVA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 11:40:48 GMT</t>
+          <t>Wed, 01 Apr 2026 10:47:41 GMT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxPWHU0dllKMlNxUkJiVWI0M3RFMkxUZlpVZHhMcDVTal9rQzVua3BEQ2Y5NGtqbnRzSEhpTXdTUFUzTlZWQV9qQlFjUUotWkVHaDVvaV9DbjY0dEY5TG1HOHczZE5mZ3hoM3lVckJqUmFfXzM4dkVCWFF0Z2tQbkEyVkFvZVJpZjJyQ21ocVotYmFjc2FRbjdoZmpUa2xic2Z5UHd1YVhTcDh4QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxQZmxiWlBGTjBrQnJtNnJMYUl1aW5adE9VaXlnOFViUkwwOWp6bHptS3FtQlVkMkVzTnR5YnZRbkQtOFRmbU9kXzZNV3psSUV0cjZNSk9aOVZEVGZzOXhMYzJDeUtXWGlabzBwQTFjajNQZVZJaG9wUHhHQXJ4WXk2VF9nRHB1OV9zUmJpTGtnakY4WU4wYzI1TXNQMjh3YVZRREZGU0lKa3FhMDMzQzdqN1lCRDJsdkdzazdxZEpVQS1VSTB1Y05TOXF2UW81TWRzR05rTWNDajVWZkR5N1lzeFhR?oc=5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46113.48666666666</v>
+        <v>46113.44978009259</v>
       </c>
     </row>
     <row r="17">
@@ -1315,22 +1315,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jongen uit Friesland wilde aanslag plegen op Vlaams Parlement in Brussel - NRC</t>
+          <t>“Iemand die 1.500 euro wil verdienen?”: hoe een 13-jarige Nederlander een aanslag op het Vlaams Parlement plande - HLN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Boy from Friesland wanted to attack the Flemish Parliament in Brussels - NRC</t>
+          <t>“Someone who wants to earn 1,500 euros?”: how a 13-year-old Dutchman planned an attack on the Flemish Parliament - HLN</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 09:19:10 GMT</t>
+          <t>Wed, 01 Apr 2026 21:04:48 GMT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiugFBVV95cUxQQzdqendJRW13bzNLejlNYk9zMU1oQ0d0c0ZGQy0zS3JsU25YN3dPcFhaQVk1Vl9pc3U3Zlg0aE9mYnRhNzI3Rm5ucnZGUHRobHNIaVR0aVFkb0ZubWRkNVFrVEQtOXBGU1ZVRnZkSWtnUklpZW94SjJrMkk0RThVbE50V0RIc3ZOOFBXVFQ5M1owa3lWSkl1d3RqUHB5aGg1b0I0YzRXcXUxdDJ2X1VscjFIdFZPQVpuYXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOUW9WTG9iN3E4SWYzOUNTc1NxREIxSFlBSjM2RUlZTUlMZzdHa0RRTnZzTnJvbzJwclJmTVpwNWh4OFFjTUhrdUNhd3hIZjRidk10X0JEbzc1bTY4T25paTFPVXdOX2tGVTdZVlRoaFFicHBLZzE1ZmxXSUxHNlI5bTROX3BFSy1sUmhER19iT0pXMS12eXgxY1ZsYmhiRTFMX0xNNUEtTUdtM21icC1MTVk2aGkyZE1uaWo3ZXh0ajRDMVhUVldqMm1aNlVzQjdqMUh2SFgtSzE3NDVXck4xMU5R?oc=5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46113.38831018518</v>
+        <v>46113.87833333333</v>
       </c>
     </row>
     <row r="18">
@@ -1370,22 +1370,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>“Ze is dagenlang geterroriseerd, gestalkt en belaagd door die vrouwen”: rechtbank oordeelt zwaar over dames die explosief naar voordeur van vriendin gooiden - pzc.nl</t>
+          <t>Kennedytunnel volgende week twee nachten gesloten voor onderhoudswerken - Nieuwsblad</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>“She was terrorized, stalked and harassed by those women for days”: court judges heavily about ladies who threw explosive at girlfriend's front door - pzc.nl</t>
+          <t>Kennedy tunnel closed for two nights next week for maintenance work - Nieuwsblad</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 18:32:00 GMT</t>
+          <t>Wed, 01 Apr 2026 11:22:07 GMT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwJBVV95cUxPNmdLQ1dmOU12dHg5bWxRbWxrWmZOb3AtckVaRnNzejZtOHlETEhmXzI0N0duNzloNlZxd2N0X2F5Q05NaHlydnhBdDAxcjVfT3g0LW5ESlo4RXdTSWoxQlR2UkNVZUZfRFU5R3ZhWE9VRjRFU09vNE1faUs1cXFUZi16M09id2NZZDBVVEY5bFBvblFaNDNENUE1QkZiS1FkNGl0SGhUMGwtYXpITlZLaDl6QzNNelh1Zmc3RHFoRXUyeTdGbGhzSWtmM3BVSVpHVFZtMmZVa0xaR0FSZWJvTFlZX3k1Z2FIbWVPNWpkdms3RUpWcUswU05nZ0tDQU5EeVdrZ09RU0RnVnZOMVA3b0VQMkU1LVdXc3VV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQWEx3d0FKT0ZIaWNjT1lLb0Ftb1FjRXEzaTlKTlBhcjMxOWtEYmRzdFEtYUFqV2p3WUlfMGNlT0pwS0Eydk9ONm1PeXhBSjJRZHF1bVAzMnlabGlfRFd2MEUxQVNuaS1aN2NOYlY4Rkdnc2FFZjE4alRRNTl6MVNSVmJ0YmM4SmVUamxjWV9SUmk5NWdQb1JOdEtHUTRscUpJc0ZBTGVxM0hqeUo4RFlRWnlfYWl0bVItOXMxVXEzS0h0Q3BjVllfanh1ejVPM2VJbVEtS05xRzV3Y01ZWkRNeDlOb2otRktqQnc?oc=5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46113.77222222222</v>
+        <v>46113.47369212963</v>
       </c>
     </row>
     <row r="19">
@@ -1425,22 +1425,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>“Iemand die 1.500 euro wil verdienen?”: hoe een 13-jarige Nederlander een aanslag op het Vlaams Parlement plande - HLN</t>
+          <t>Na dag staken, rijden buschauffeurs donderdag terug uit in stelplaats De Lijn in Mortsel: “Na paasvakantie verder onderhandelen” - Nieuwsblad</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>“Someone who wants to earn 1,500 euros?”: how a 13-year-old Dutchman planned an attack on the Flemish Parliament - HLN</t>
+          <t>After a day of strikes, bus drivers return to the De Lijn depot in Mortsel on Thursday: “Continue negotiations after Easter holidays” - Nieuwsblad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 21:04:48 GMT</t>
+          <t>Wed, 01 Apr 2026 16:07:15 GMT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOUW9WTG9iN3E4SWYzOUNTc1NxREIxSFlBSjM2RUlZTUlMZzdHa0RRTnZzTnJvbzJwclJmTVpwNWh4OFFjTUhrdUNhd3hIZjRidk10X0JEbzc1bTY4T25paTFPVXdOX2tGVTdZVlRoaFFicHBLZzE1ZmxXSUxHNlI5bTROX3BFSy1sUmhER19iT0pXMS12eXgxY1ZsYmhiRTFMX0xNNUEtTUdtM21icC1MTVk2aGkyZE1uaWo3ZXh0ajRDMVhUVldqMm1aNlVzQjdqMUh2SFgtSzE3NDVXck4xMU5R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNNWdvZXhQbDNmLUw4RklCeXg1cjl6M1doV1AxZ2VyTndUOVNaSFlSczZFNGlubkpwZDZoY1BwYjFHSTVnTm9TNnNBUHF6RWNuYm5HVW52cmdWWTNUT29ZbmRfb3hyNTBONFVYMG5pUEJ5d0tHNFlXM1Rscm93TVpsOFJHRE5rN2dhZlNvVk1ieUhZaHBoQXpGamF2TGZpTHM2OU1TMEI0ODZVQlBQWFdGTzFyR0l0bTdhWTdBRTZvMTlGTHdpMUF5bnVpa3AxS3VDU0k0OXpiZE1pZGNWcHFMYU1ueXN6OFl0UXQ5bTJUaURVZDFKbjRmZGoyTV8ybHdRTHR5b3NrNHpfQWlpS3UzRUkyVTktSk9uZFlYcmNja0ItTzV2ZWJfankyQU5SLWhM?oc=5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46113.87833333333</v>
+        <v>46113.67170138889</v>
       </c>
     </row>
     <row r="20">
@@ -1480,22 +1480,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tiger Woods wil zich laten behandelen na arrestatie in Florida - HBVL</t>
+          <t>Minderjarige jongen veroor­deeld voor voorbereiden extreemrechtse aanslagen in Nederland en België - de Volkskrant</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tiger Woods wants treatment after arrest in Florida - HBVL</t>
+          <t>Underage boy convicted of preparing far-right attacks in the Netherlands and Belgium - de Volkskrant</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 07:11:46 GMT</t>
+          <t>Wed, 01 Apr 2026 12:03:59 GMT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPZDg5bXdnMndQTVY5RzByb1I4MkF6ZkRJdjRDOWpQdHVQSExveGZjNXZZMTVwWlE2Nm1mTDFRbF9rQjBCQ2k4UmQ4QmNUOC1YWV92bnRVTFMyRFFXMjM2aFpqVWJfOFlaN2IxSTFPRjBQNF9VNmZfNHhSVF82OXpoakl6Ri1CSXYyU01GaTJDLWhwWVBtQUZHUWVydlp1eVN5aUd0Sm1GcmpaWDVHTWFvaGxPYUtUZkowOUE4ckgybWE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQcVRVTU5mSjBXdWZNbG1WdG5ZU21hdDVTOEp6NWhqN2FXOEM4aXNkdjdNMktZVEIyYXFIRUgxYXRQX2Q1MXNOTlkwRzB0MWZWRHgxbXFBV2JEanV5eTVkc0NvVElvbUVIaFI3OEoxTWNWc2k5blAtcUpXOFFRM1EwX1RlZFNSdGI3MWJiWHUyQlI0ZnBJNmI1TWhOeTRHbTFiZW1LdTN3YThnb0hhX29uWDFWXzV2SHhHdEpNd3BySUZmbUwzeWhFbXJNbHdjQnl5SVd3RThrYTF0V19TREE?oc=5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46113.29983796296</v>
+        <v>46113.5027662037</v>
       </c>
     </row>
     <row r="21">
@@ -1535,22 +1535,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morgen opnieuw bussen in regio Antwerpen nadat buschauffeurs spontaan werk neerlegden aan stelplaats in Mortsel - VRT</t>
+          <t>Pro-Palestinademonstranten bezetten universiteitsgebouw bij ziekenhuis in Maastricht - stadindex.nl</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Buses again in the Antwerp region tomorrow after bus drivers spontaneously stopped work at the depot in Mortsel - VRT</t>
+          <t>Pro-Palestinian demonstrators occupy university building near hospital in Maastricht - stadindex.nl</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 09:47:35 GMT</t>
+          <t>Thu, 02 Apr 2026 09:05:30 GMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNeHBXZU9TeTJBUTRVSzFaOVhiYjFrSUg4OGk0cEFLMjMzTUJXclU2a2JRY081VlZlLXFUTjZUcHNscE9EbXpVbm56VWhPVmJONnhGekE0ekNuVzZ4UUd4dFZtckFZaHdXcnVSMVNnUy1aS0lDMlo4R3E3Tlc5Wmd2a1hR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxNWHRoSVRvVDNrUTZkS0J3ZjRZeWMzWUFIUi0zY1JvYmUxdmRpeEN5RU0ybXRLOVJyNnpJSTI4WjhaeHhxVlR4aWhhbkwyWHdrNG1nZk5CVFJUb3l0cGRnaV9kMmR3Y2lIUWtZU3BSYnYwOUlKSl9mUlAzelNpRzFSRmdDVGRVX3BZLTd2cmc2bUhUVkpnM2RqZmdlM09GeXR6SGdGRlZKOW01Qjh3eGlj?oc=5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1574,38 +1574,38 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46113.40804398148</v>
+        <v>46114.37881944444</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kennedytunnel volgende week twee nachten gesloten voor onderhoudswerken - Nieuwsblad</t>
+          <t>Europol links extremist propaganda to terror acts as man sentenced to 20 years - The Brussels Times</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kennedy tunnel closed for two nights next week for maintenance work - Nieuwsblad</t>
+          <t>Europol links extremist propaganda to terror acts as man sentenced to 20 years - The Brussels Times</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 11:22:07 GMT</t>
+          <t>Wed, 01 Apr 2026 21:27:06 GMT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6gFBVV95cUxQWEx3d0FKT0ZIaWNjT1lLb0Ftb1FjRXEzaTlKTlBhcjMxOWtEYmRzdFEtYUFqV2p3WUlfMGNlT0pwS0Eydk9ONm1PeXhBSjJRZHF1bVAzMnlabGlfRFd2MEUxQVNuaS1aN2NOYlY4Rkdnc2FFZjE4alRRNTl6MVNSVmJ0YmM4SmVUamxjWV9SUmk5NWdQb1JOdEtHUTRscUpJc0ZBTGVxM0hqeUo4RFlRWnlfYWl0bVItOXMxVXEzS0h0Q3BjVllfanh1ejVPM2VJbVEtS05xRzV3Y01ZWkRNeDlOb2otRktqQnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQcUpfcndwbnk1dXNFUW9xOGZzWEctQmZQbElrZ2V6TFMzYUJBeHhSeXVrczFqUk9nbHN1Xzd4aEt4My1mOFZyWDBYa1IwODJaYkVZem9lVGltanppbTNub0ZYb3RIWXZHeGtvSUJjNTNnaXZfX2dWa19ZdVdYZzBTcUUtcER1ekliS282aVBLcWtsRjNIcDZHWFhWTEJXYjVxdWg3QWpwcExsUnFDQ2hJWlhhTXdZWnc?oc=5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1625,42 +1625,42 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46113.47369212963</v>
+        <v>46113.89381944444</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jongeren op de vlucht na politieactie in Hoboken, droneteam leidt tot arrestaties - GVA</t>
+          <t>St. Lawrence Co. man dies following crash - wwnytv.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Young people flee after police action in Hoboken, drone team leads to arrests - GVA</t>
+          <t>St. Lawrence Co. man dies following crash - wwnytv.com</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 08:48:23 GMT</t>
+          <t>Wed, 01 Apr 2026 17:48:00 GMT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9wFBVV95cUxOVm9YbDFzLWwxRmRMbU9INlh6MzhobkRITWxoZ3dPdkowTmprajd4UzRoS2d5YllTQ0VxMXhSZHBmQXJrSS11d2RpZGNqNS1jN0hmOFYxX2RqVFd0QWdSY1FHQVpwaFpqR1JYVUxDOGp0QlhyLVVrZUVHUFUwZHFETGJwSmdMRnZ5NjBOcjdUQzdVdmZsOVExU3NmSjhIUmljMFFuTlBrLTN5Z1IySmEzbkw1S0IyWDJQVXpsMk9iaVdFa0VTTUR5SEQwQUg4a3N6NGlydzZtbUd1aS0zTWtfMmxxODNHVVlDTWJ5S21DZEpaSXhWeGNz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNVmlnWm91b0FWNE9fMDIzVFF3b3p1VmpEd1picDVZeFprV2s0OTMxZlFLV1UxTnBHWkVGTGlHaVFibmczZGhTd1RMQ0hKWHZOX0tOcXJtQ0lfU0dHcWkyajRGeWhXRkV3ZHFkTXJHOVlOT3ZnMG5pajczYTFxTUw5VnhPR3pka2xrREJFMW81ZXVUV0HSAZMBQVVfeXFMTVZpZ1pvdW9BVjRPXzAyM1RRd296dVZqRHdaYnA1WXhaa1drNDkzMWZRS1dVMU5wR1pFRkxpR2lRYm5nM2RoU3dUTENISlh2Tl9LTnFybUNJX1NHR3FpMmo0RnloV0ZFd2RxZE1yRzlZTk92ZzBuaWo3M2ExcU1MOVZ4T0d6ZGtsa0RCRTFvNWV1VFdB?oc=5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1680,42 +1680,42 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46113.36693287037</v>
+        <v>46113.74166666667</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Na dag staken, rijden buschauffeurs donderdag terug uit in stelplaats De Lijn in Mortsel: “Na paasvakantie verder onderhandelen” - Nieuwsblad</t>
+          <t>Trump assures that he is “about to” achieve “all” his objectives in Iran: “We will return them to the Stone Age” - democrata.es</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>After a day of strikes, bus drivers return to the De Lijn depot in Mortsel on Thursday: “Continue negotiations after Easter holidays” - Nieuwsblad</t>
+          <t>Trump assures that he is “about to” achieve “all” his objectives in Iran: “We will return them to the Stone Age” - democrata.es</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 16:07:15 GMT</t>
+          <t>Thu, 02 Apr 2026 02:52:00 GMT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisAJBVV95cUxNNWdvZXhQbDNmLUw4RklCeXg1cjl6M1doV1AxZ2VyTndUOVNaSFlSczZFNGlubkpwZDZoY1BwYjFHSTVnTm9TNnNBUHF6RWNuYm5HVW52cmdWWTNUT29ZbmRfb3hyNTBONFVYMG5pUEJ5d0tHNFlXM1Rscm93TVpsOFJHRE5rN2dhZlNvVk1ieUhZaHBoQXpGamF2TGZpTHM2OU1TMEI0ODZVQlBQWFdGTzFyR0l0bTdhWTdBRTZvMTlGTHdpMUF5bnVpa3AxS3VDU0k0OXpiZE1pZGNWcHFMYU1ueXN6OFl0UXQ5bTJUaURVZDFKbjRmZGoyTV8ybHdRTHR5b3NrNHpfQWlpS3UzRUkyVTktSk9uZFlYcmNja0ItTzV2ZWJfankyQU5SLWhM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOdVZScTNqcWxlZHQ2dkRObWg4VWlYOExxS1p6aDVuVFRramNEQUVsTXd6UFkzalRPRFZYRUw1aEN2RmpjRjJlOHh3ZklhRVp2bDZxYlQ0Nm51NGpTZ1dPa0NXU0k1d3RfS3FEREhKRWRJUTlDV2Y4OUJMcFBRamhsZ25ycU9KZ0liMjdYclVvLXRlQ3J30gGaAUFVX3lxTE1rc3BxcW4tUWNCY0lWaWkxdHBDaUx1OF8wR1NXOVRNLW1VTGV2LWtwWnRCOWF6TldvNHRxNU5idi1MU1VKcWhqZnBNZF81M2ZEekxZTXJ3YXZfNjFmVGoxSjdFeExjVkduOEh6ajh2bDBFTUdzejBfNjdnbDAwa3o5U3g0MHNGRzh4emFLdlNSc3Y5ZHE2TFNOWnc?oc=5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1735,42 +1735,42 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46113.67170138889</v>
+        <v>46114.11944444444</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Minderjarige jongen veroor­deeld voor voorbereiden extreemrechtse aanslagen in Nederland en België - de Volkskrant</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Savannah Guthrie's first interview since the disappearance of her mother - 9Now</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Underage boy convicted of preparing far-right attacks in the Netherlands and Belgium - de Volkskrant</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Savannah Guthrie's first interview since the disappearance of her mother - 9Now</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 12:03:59 GMT</t>
+          <t>Thu, 02 Apr 2026 04:41:46 GMT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQcVRVTU5mSjBXdWZNbG1WdG5ZU21hdDVTOEp6NWhqN2FXOEM4aXNkdjdNMktZVEIyYXFIRUgxYXRQX2Q1MXNOTlkwRzB0MWZWRHgxbXFBV2JEanV5eTVkc0NvVElvbUVIaFI3OEoxTWNWc2k5blAtcUpXOFFRM1EwX1RlZFNSdGI3MWJiWHUyQlI0ZnBJNmI1TWhOeTRHbTFiZW1LdTN3YThnb0hhX29uWDFWXzV2SHhHdEpNd3BySUZmbUwzeWhFbXJNbHdjQnl5SVd3RThrYTF0V19TREE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNV3RTc25YbGd0WXJYV29WOHpiNTZwckJwQi1OM0oySXNFZUFMMzdwQXFXX2hzUWZqSGdfNTBUb1JoV0Y1N19tQkVKaTNjS0dsdFdWbWZMSkxxWjE0bWxnTlRNT1NOTExzMm11RFpuakJ5eXQtdURkTl9NckJUS1ZQellBTDVTUkpJNWc2eA?oc=5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1790,11 +1790,11 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46113.5027662037</v>
+        <v>46114.19567129629</v>
       </c>
     </row>
     <row r="26">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europol links extremist propaganda to terror acts as man sentenced to 20 years - The Brussels Times</t>
+          <t>Dutch schoolboy convicted of planning terror attack on Flemish Parliament in Brussels - The Brussels Times</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Europol links extremist propaganda to terror acts as man sentenced to 20 years - The Brussels Times</t>
+          <t>Dutch schoolboy convicted of planning terror attack on Flemish Parliament in Brussels - The Brussels Times</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 21:27:06 GMT</t>
+          <t>Wed, 01 Apr 2026 12:56:24 GMT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQcUpfcndwbnk1dXNFUW9xOGZzWEctQmZQbElrZ2V6TFMzYUJBeHhSeXVrczFqUk9nbHN1Xzd4aEt4My1mOFZyWDBYa1IwODJaYkVZem9lVGltanppbTNub0ZYb3RIWXZHeGtvSUJjNTNnaXZfX2dWa19ZdVdYZzBTcUUtcER1ekliS282aVBLcWtsRjNIcDZHWFhWTEJXYjVxdWg3QWpwcExsUnFDQ2hJWlhhTXdZWnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPWUpnS3BmLUtKanJPa1N4Q19hV3Z0M2NCYnh6c3RQTzBXQklTZGh6eFdkMGJpbmVnNkptZVpLNTEzZEFmRHFMbFNSaGNxeWVtcUQweGtPYl9zcTJUcXZCTmNwM0tSX1pQdS1FN0JjNl9JbFo0bW1wWTJEUnZTLVhZVWtiR2xNMFBYemQ5LVR1TWhrMUhXUjZZT1JqLXRFN3NEd1luUXk1UGRzNVBZRXkxWE9GdEJEWVdpUkZGWXU4RXY?oc=5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46113.89381944444</v>
+        <v>46113.53916666667</v>
       </c>
     </row>
     <row r="27">
@@ -1865,22 +1865,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>St. Lawrence Co. man dies following crash - WWNY-TV</t>
+          <t>Brussels introduces nighttime closures to combat crime around North Station - belganewsagency.eu</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>St. Lawrence Co. man dies following crash - WWNY-TV</t>
+          <t>Brussels introduces nighttime closures to combat crime around North Station - belganewsagency.eu</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:48:00 GMT</t>
+          <t>Wed, 01 Apr 2026 11:01:00 GMT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxNVmlnWm91b0FWNE9fMDIzVFF3b3p1VmpEd1picDVZeFprV2s0OTMxZlFLV1UxTnBHWkVGTGlHaVFibmczZGhTd1RMQ0hKWHZOX0tOcXJtQ0lfU0dHcWkyajRGeWhXRkV3ZHFkTXJHOVlOT3ZnMG5pajczYTFxTUw5VnhPR3pka2xrREJFMW81ZXVUV0HSAZMBQVVfeXFMTVZpZ1pvdW9BVjRPXzAyM1RRd296dVZqRHdaYnA1WXhaa1drNDkzMWZRS1dVMU5wR1pFRkxpR2lRYm5nM2RoU3dUTENISlh2Tl9LTnFybUNJX1NHR3FpMmo0RnloV0ZFd2RxZE1yRzlZTk92ZzBuaWo3M2ExcU1MOVZ4T0d6ZGtsa0RCRTFvNWV1VFdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNaENpdWdTS2UxTmRFeDF2b2ZXOHM4Rk5Tc042TTVVbU96SlVTRkc4VGticTNlX0M3blJsUTUyUk9IY1FQQU9HU3NRRUJVTDRGd0J5SVltMXg0WGhZM0FjTHJ6WFdzMWRnVlg0OFltenJkbklzWmVScjFfTWpaNGVsV2pncXlBNlhCdzRSRXN5ZFByTWxNZ1h1WncxeDVWQXk0RkZ6YkdJOWNQZw?oc=5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46113.74166666667</v>
+        <v>46113.45902777778</v>
       </c>
     </row>
     <row r="28">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Trump assures that he is “about to” achieve “all” his objectives in Iran: “We will return them to the Stone Age” - democrata.es</t>
+          <t>One dead and several injured after explosion and fire in a cafeteria in Almería - democrata.es</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Trump assures that he is “about to” achieve “all” his objectives in Iran: “We will return them to the Stone Age” - democrata.es</t>
+          <t>One dead and several injured after explosion and fire in a cafeteria in Almería - democrata.es</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 04:20:46 GMT</t>
+          <t>Wed, 01 Apr 2026 16:58:00 GMT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOdVZScTNqcWxlZHQ2dkRObWg4VWlYOExxS1p6aDVuVFRramNEQUVsTXd6UFkzalRPRFZYRUw1aEN2RmpjRjJlOHh3ZklhRVp2bDZxYlQ0Nm51NGpTZ1dPa0NXU0k1d3RfS3FEREhKRWRJUTlDV2Y4OUJMcFBRamhsZ25ycU9KZ0liMjdYclVvLXRlQ3J30gGaAUFVX3lxTE1rc3BxcW4tUWNCY0lWaWkxdHBDaUx1OF8wR1NXOVRNLW1VTGV2LWtwWnRCOWF6TldvNHRxNU5idi1MU1VKcWhqZnBNZF81M2ZEekxZTXJ3YXZfNjFmVGoxSjdFeExjVkduOEh6ajh2bDBFTUdzejBfNjdnbDAwa3o5U3g0MHNGRzh4emFLdlNSc3Y5ZHE2TFNOWnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOaWZMRmROMURLZlRzU2I4VGJLVkdCY242UzN2SnhUQ2dnWXQwbjFxcU5iV0RfMTJycEZEUGdQeGd6NGpfRzM3ajUxbzdpRFl2TWZHbnBHWm9hbDdrQ2paTVplTjdBX3VXOURYVnNPcEt1QkRpenc1aDg5SWZjTU9OQ19kYzMtaC1NaXJkdVhZNHJQZ2lGd2pISnZkNW9ScjJFMzJvNS01SUhEWU96LTBUY2RleG1zbl9aNzhFdUUzb1PSAcYBQVVfeXFMT3pjSzRxT3JSdHAtb3BLYlczQzdJaXZqMk5ZVHFDcXc1cXdTRVZ0U2VsSU9WYnZqMTBhZlphX1FUMmxxXzQ5S0ZMSG5EalVPZHVEQm1BNy1IWWI2SmdQQkpGQzNQWTJ0WGh6MWI0Q2NWLVh4N3hHYTJabTdXZWZodUg5eFpCenlfcW9jMm9YelhEMWM4Ukx1VGg2UVpQT0ZwV3JnVDAxanlsQlJfbm5PRzk0MzBmbHg4Ym50a04xM0hMZ1QwZkxn?oc=5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46114.18108796296</v>
+        <v>46113.70694444444</v>
       </c>
     </row>
     <row r="29">
@@ -1975,22 +1975,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dutch schoolboy convicted of planning terror attack on Flemish Parliament in Brussels - The Brussels Times</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Hunt for Pokémon bandits after cards stolen - 9Now</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Dutch schoolboy convicted of planning terror attack on Flemish Parliament in Brussels - The Brussels Times</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Hunt for Pokémon bandits after cards stolen - 9Now</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 12:56:24 GMT</t>
+          <t>Thu, 02 Apr 2026 07:16:01 GMT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPWUpnS3BmLUtKanJPa1N4Q19hV3Z0M2NCYnh6c3RQTzBXQklTZGh6eFdkMGJpbmVnNkptZVpLNTEzZEFmRHFMbFNSaGNxeWVtcUQweGtPYl9zcTJUcXZCTmNwM0tSX1pQdS1FN0JjNl9JbFo0bW1wWTJEUnZTLVhZVWtiR2xNMFBYemQ5LVR1TWhrMUhXUjZZT1JqLXRFN3NEd1luUXk1UGRzNVBZRXkxWE9GdEJEWVdpUkZGWXU4RXY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPdUVzS1hYdU1vOWRiZElyYjVKRmJ3M0VXNXRpT1prWVQySDFQQkdxZVpXb25zLXRBc3gtM3V4dkpsSGtNRWtvNnhBb1dWcGI4elFvWVlubGFWQXJQQ0xhbWd4Q3FZdFV3RTBsaU96UFNSbVdWOVlQTnN1VzN1c1ZMNnQwb0xYYjNYY2JaeQ?oc=5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46113.53916666667</v>
+        <v>46114.30278935185</v>
       </c>
     </row>
     <row r="30">
@@ -2030,22 +2030,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - Savannah Guthrie's first interview since the disappearance of her mother - 9Now</t>
+          <t>Clean up Brussels - The Brussels Times</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - Savannah Guthrie's first interview since the disappearance of her mother - 9Now</t>
+          <t>Clean up Brussels - The Brussels Times</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 04:41:46 GMT</t>
+          <t>Wed, 01 Apr 2026 23:21:50 GMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNV3RTc25YbGd0WXJYV29WOHpiNTZwckJwQi1OM0oySXNFZUFMMzdwQXFXX2hzUWZqSGdfNTBUb1JoV0Y1N19tQkVKaTNjS0dsdFdWbWZMSkxxWjE0bWxnTlRNT1NOTExzMm11RFpuakJ5eXQtdURkTl9NckJUS1ZQellBTDVTUkpJNWc2eA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgNBVV95cUxNM1BEc19JV2ZmbkxtMkxLemNWbmtyVmoxS2RfeUdfdWE0Z2M4MVZBUXlSMUowY0NlNWttS2dIbHBlSE81emxEY015WGFaR0VneDFxNTZxT1YxX1hkLWlrTjlXQnRYdV9TYWpDbUcyUjVXdVlCZUpGTzdudUVVSzFrMWlmVUhOUFM0RHFHejI3dGppUWFvQWdjbG9qemhLYlhwalZxd25ZZHBrRERod1VxZnAtQmhsZjhVVkpQa0IzLVh5clNoTTZKMWs2T2ZyTmpJLTNSdEZRNGZNb05SNkN6eVF1NUVpcjFhLXBoZ214QlBBenVVWndtc0pQZWxZZ2NKYjFaajZsQWlLaERURU9DcEltR0k5dkg4blhIRTdWd2d3cDl2cmVzY2xDeWZCbk90OG1fOUZvQzZzZGpuNGlpNlE5dFNpbGxUUzJrS0lWSDZ3RU1WNm54YnpwS3ZZM1ZIZjRqQ0lGMWF6M1pBckNtQkhkRXA0U045NTFSeVFiY1piMlRBYVdKZkJFMDRtaUhXSGVPWUhqT1Rrb3JPTVpUWGhyTnRhMG5VYkFPTGN3aGIzTk9mNVE?oc=5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46114.19567129629</v>
+        <v>46113.97349537037</v>
       </c>
     </row>
     <row r="31">
@@ -2085,22 +2085,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brussels introduces nighttime closures to combat crime around North Station - belganewsagency.eu</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Are granny flats the solution to affordable housing? - 9Now</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Brussels introduces nighttime closures to combat crime around North Station - belganewsagency.eu</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Are granny flats the solution to affordable housing? - 9Now</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 11:01:00 GMT</t>
+          <t>Thu, 02 Apr 2026 07:14:56 GMT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxNaENpdWdTS2UxTmRFeDF2b2ZXOHM4Rk5Tc042TTVVbU96SlVTRkc4VGticTNlX0M3blJsUTUyUk9IY1FQQU9HU3NRRUJVTDRGd0J5SVltMXg0WGhZM0FjTHJ6WFdzMWRnVlg0OFltenJkbklzWmVScjFfTWpaNGVsV2pncXlBNlhCdzRSRXN5ZFByTWxNZ1h1WncxeDVWQXk0RkZ6YkdJOWNQZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxPUURfVVNjNElzaW1ERWl2aXpVWmgyWnFSV2I2U1hnWUZodFVTdFpCM2JHVnFlQVdaNUw2d0JuVDBncHRmaGsyV093cGtYQ25HTy1qa2Vxc3l5OG84WnZFbnk4OXZJWjNjcUtJdGUyTzR5UzNLSnAtNi1OcjFnNElLNXdwR3RNdUROa2VNSg?oc=5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46113.45902777778</v>
+        <v>46114.30203703704</v>
       </c>
     </row>
     <row r="32">
@@ -2140,22 +2140,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>One dead and several injured after explosion and fire in a cafeteria in Almería - democrata.es</t>
+          <t>Women get suspended sentences for fireworks attack - The Brussels Times</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>One dead and several injured after explosion and fire in a cafeteria in Almería - democrata.es</t>
+          <t>Women get suspended sentences for fireworks attack - The Brussels Times</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 16:58:00 GMT</t>
+          <t>Wed, 01 Apr 2026 20:14:35 GMT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOaWZMRmROMURLZlRzU2I4VGJLVkdCY242UzN2SnhUQ2dnWXQwbjFxcU5iV0RfMTJycEZEUGdQeGd6NGpfRzM3ajUxbzdpRFl2TWZHbnBHWm9hbDdrQ2paTVplTjdBX3VXOURYVnNPcEt1QkRpenc1aDg5SWZjTU9OQ19kYzMtaC1NaXJkdVhZNHJQZ2lGd2pISnZkNW9ScjJFMzJvNS01SUhEWU96LTBUY2RleG1zbl9aNzhFdUUzb1PSAcYBQVVfeXFMT3pjSzRxT3JSdHAtb3BLYlczQzdJaXZqMk5ZVHFDcXc1cXdTRVZ0U2VsSU9WYnZqMTBhZlphX1FUMmxxXzQ5S0ZMSG5EalVPZHVEQm1BNy1IWWI2SmdQQkpGQzNQWTJ0WGh6MWI0Q2NWLVh4N3hHYTJabTdXZWZodUg5eFpCenlfcW9jMm9YelhEMWM4Ukx1VGg2UVpQT0ZwV3JnVDAxanlsQlJfbm5PRzk0MzBmbHg4Ym50a04xM0hMZ1QwZkxn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNQWxNcExTalhUaUViX2xUSmZNdXYxQnVaT3RfMUY2MHRZLXJuT3ZZZUhpXzk1ajlxdHlCMUNGREF1Mnp2SXNsMVRvM0ktVkhjVkY5TnJ0amwzaGJiRU1LQmFFYW9Vaml4ZUNZeDJnOWJPeW14MjNCdWc5clBQLURsQUotWEQ4VlZfN045VmNaVFdFaHEtczlHcDRQdDR5QQ?oc=5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46113.70694444444</v>
+        <v>46113.84346064815</v>
       </c>
     </row>
     <row r="33">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Clean up Brussels - The Brussels Times</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Opposition pushes to half fuel tax temporarily - 9Now</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Clean up Brussels - The Brussels Times</t>
+          <t>Watch 9News Latest Stories - Season 2026 - Opposition pushes to half fuel tax temporarily - 9Now</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 23:49:36 GMT</t>
+          <t>Wed, 01 Apr 2026 21:00:13 GMT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitANBVV95cUxQUVpoUndLeTV2ZEF1UXNCaF8tY2NoUVUtYUtIRzdLOVZTUGJsLXdaSVJLc1lESTRsRGMwOTVQdW1SRXk3LVRUMHlvcm9TQm1fdXk1R0hKUm1ZN0s3d2V2QmxIVWZFZ2xjU21yWS0taXdfWDBYNjBJbFZGczh3NEFRTld0Ni1xOTV6ak9ESWFBeDVQTlNvVnBQWE1hQlA5VklRcWh5bmRWb0p4MGI1Sm9PY2NudWd1b00xdjlENmYxNDFFM3NFWFZVa1FPSmd2ZUwwZklFWVYxQzhISDV2eTZ0ci1jSEM5NTgtNTlpb0JZaHZHX3RGYlJZMnNrN2c4Vk9PVjJBSktkb3Atb1oyQjBkSENacXlSbzBYS0dHQ19oemZEb0puV1paOFhVUFVudHM5TnBYQ2RyVGFnVkpOVmxJT01ReTVfZkFBbVJNNXQtYUJYRFhQOHJlTFNNWUhPYTVrNWZZX3JnZTlrZGRMcW5kNzlTZFNvYXczdFlWSk5PRG5HaWo4NzhkVTZPOGlIUkltaFF0WHY3bEpIcW40Q2k1b3d0TGVMcW1BOUgtR2w3TkpZUkhQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOLXlfakREcGxBeE42Q1dMVWxndHlmcHNocDBtVFVobFhjRmo1WWVBNVJQZlBtTzFvM1NqZ2Q1dGVuakhFNlRabS1XTVdvdG9qSi1zX0VGNU9reGpFV0Q2WEEtekVLM21keWFwWmdQMXdsREJxb01xNVJlUG5SSV9sYUF1MGoyMlZIc25FYw?oc=5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2234,38 +2234,38 @@
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46113.99277777778</v>
+        <v>46113.87515046296</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - Government sets sights on blackmarket tobacco with tough new laws - 9Now</t>
+          <t>Dossier Sky ECC : 15 ans de prison en appel pour Abdelwahab G. - BruxellesToday</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - Government sets sights on blackmarket tobacco with tough new laws - 9Now</t>
+          <t>Sky ECC file: 15 years in prison on appeal for Abdelwahab G. - BruxellesToday</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 03:02:46 GMT</t>
+          <t>Thu, 02 Apr 2026 09:42:00 GMT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNMTRrMnFHUEJNdk82eVlUZEV4SjY2dThmSnFjd2pKSTQtRTNRSUg1MXZyd0hkejMzVDhkc0U0dEdpdkpJVjExa280SGY0V1ItOUVJRnFLYmdFUmVyNHhSc21rZWR3aWMzTENjb2lldDhIMHpBTjhtWnRwZlFfWnlPYTkxdHYxcFRVOEREeQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQQmUwU1BLd3hQeFA2N3NmZENtQ3ByQ01jTk5ybm9XYS1wQUVNMm9ORUoxeW0wdlc1OWZ2QU0yVlJTNkhtazlLZVJXeWdyOXZhZVRxMWd1Q1ZCaDZKclpLcVpxZVI3STJCTC1aVERYcUdORE8wclE1Qk5GdmpMcTJDVGZuNTN2X1Zud3RlVmRGWQ?oc=5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2285,42 +2285,42 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46114.12692129629</v>
+        <v>46114.40416666667</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - Opposition pushes to half fuel tax temporarily - 9Now</t>
+          <t>Un homme interpellé après avoir brandi un couteau à l’hôtel de ville de Roulers - 7sur7.be</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Watch 9News Latest Stories - Season 2026 - Opposition pushes to half fuel tax temporarily - 9Now</t>
+          <t>A man arrested after brandishing a knife at Roeselare town hall - 7sur7.be</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 21:00:13 GMT</t>
+          <t>Wed, 01 Apr 2026 13:43:00 GMT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOLXlfakREcGxBeE42Q1dMVWxndHlmcHNocDBtVFVobFhjRmo1WWVBNVJQZlBtTzFvM1NqZ2Q1dGVuakhFNlRabS1XTVdvdG9qSi1zX0VGNU9reGpFV0Q2WEEtekVLM21keWFwWmdQMXdsREJxb01xNVJlUG5SSV9sYUF1MGoyMlZIc25FYw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNU2pFbW9GNTFZMlppRXJ5QkE0bE9mTEYwRWhnbVpUZVNtVVh3ZUtsR0tYQWtYYkx0cHg5R2J2d1g1QnpsalZZeFhHeDd1YTJBYkZHSDdEaW9Mcl9veko3cE5wMjZfVFJqWm5XOGtPTFVZMV80LTJsYXpyQVdSc09SNEwycFRFZG1CMTFPMlFObkduODNDbDdBdWR0YlJwOV9uMFhtR0pQMjJ0b3NxOU1HV1hUTW9FRHRzcWZfdUVqSQ?oc=5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2340,42 +2340,42 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46113.87515046296</v>
+        <v>46113.57152777778</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Women get suspended sentences for fireworks attack - The Brussels Times</t>
+          <t>Un député fédéral agressé par des voleurs en Belgique - Radio-Canada</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Women get suspended sentences for fireworks attack - The Brussels Times</t>
+          <t>Federal MP attacked by thieves in Belgium - Radio-Canada</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 20:14:35 GMT</t>
+          <t>Wed, 01 Apr 2026 19:49:19 GMT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNQWxNcExTalhUaUViX2xUSmZNdXYxQnVaT3RfMUY2MHRZLXJuT3ZZZUhpXzk1ajlxdHlCMUNGREF1Mnp2SXNsMVRvM0ktVkhjVkY5TnJ0amwzaGJiRU1LQmFFYW9Vaml4ZUNZeDJnOWJPeW14MjNCdWc5clBQLURsQUotWEQ4VlZfN045VmNaVFdFaHEtczlHcDRQdDR5QQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNM282YVZsekJmTktMVzBEb3VjOFBZbHZnNVNLaUp4aEJKeUF1VFZKbHZNZXlkTTBuY01ZNmltVFZFOUVQalFlWGNiYW1xNERQeFJ6YXR3R1NkLXRFSTlkVkJwOTh0ZTJyTmJfbl9JR3hPQzc4YmZvUjc0N1oyQ09laUo3SmNMc3NtOHVKd0JrMDBVNkU3?oc=5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2395,11 +2395,11 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46113.84346064815</v>
+        <v>46113.82591435185</v>
       </c>
     </row>
     <row r="37">
@@ -2415,22 +2415,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Un jeune Néerlandais de 13 ans préparait un attentat contre le Parlement flamand à Bruxelles - BruxellesToday</t>
+          <t>Grève spontanée des chauffeurs de bus dans un important dépôt à Mortsel : la région d'Anvers impactée - VRT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>A 13-year-old Dutch boy prepared an attack against the Flemish Parliament in Brussels - BruxellesToday</t>
+          <t>Spontaneous strike by bus drivers in a major depot in Mortsel: the Antwerp region impacted - VRT</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 09:01:00 GMT</t>
+          <t>Wed, 01 Apr 2026 12:14:01 GMT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxOTVZTa0ZQZWIzU2xUbzBjcXV0YUpVWnVCS2NVeXhSSFN0RnV3dEtyelZGQUk0R1hjT0JLRkNLLWdGckJhVmpKMnB1dWZad2lpR2s3cndvcGdJRy0tZEVua3NkZDUzNnpwaW9SY1BRZ09yRlBkTUFzRlZITVlHY05RVUdKQThfeGh3MERFMXNOdDhwMmdKYTZzNDR4VnBuMXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQRG1DcDRkTkRnTE54ZG45SWVoNVltZVp4bW4zOWt2YndrTjZUVksyNDk1d2ZnbmhWaVNpM1BKcE1zZVlybVgwOXVKaW5HNnh5T0xYTFJBbUNKZFI5dkstSEhwQ1loRG9odDBZWGs2NktSOEdIYUNjZlFNNEhIZGNfMVA2c3JyTGdHLWE4NkhmT0lOZks5N24yaDJIV3ZLeWZkamlpdmU2aw?oc=5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46113.37569444445</v>
+        <v>46113.50973379629</v>
       </c>
     </row>
     <row r="38">
@@ -2470,22 +2470,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Un tout jeune adolescent condamné aux Pays-Bas pour avoir planifié un attentat contre le Parlement flamand - VRT</t>
+          <t>TC Bruxelles - Un expert désigné dans un dossier d'agression à l'encontre d'un contrôleur et de policiers - MSN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>A very young teenager sentenced in the Netherlands for planning an attack against the Flemish Parliament - VRT</t>
+          <t>TC Brussels - An expert appointed in a case of assault against a controller and police officers - MSN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 08:39:30 GMT</t>
+          <t>Wed, 01 Apr 2026 13:45:57 GMT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQVHN0a2ZiYmhVSV9ieDBvWXVGdFZVZ2lueE5Bc2pFSnI3V1BGOGdEb0tsYWFVWlZYNXVKU2lfN3pEOEN1aE1uRmpzMFpjTm1hOTh2TW8zcDNXNTBCVm5GN29sbTFVcHhzXzRQUVZlaGxzV1VvbnN3NzRwSUVuMWx3S3BmY3NlaGxxbDdoaGF2RTZUZy1JOHBJMFR1eE0zQ1VGdng5OHB5Qm0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxPbWo3MW5iY0RkRVBURXJnVU5uRmo1M0ZqZHU4U3g1VG1BV0JmZ1dDNElKVnJPWmtsSzNJS3B3WFhJNktXSHMxbzVXTGlBbWlqaEk2bzBfOEpveFctZmI2b0ZGZzB1N3ZVdjU0blRfLWNkWEJwNWk4MGpycnF3MV9KQmdETWNCN3k1VFdvN0I2NTlMdWlVU2JaaE5iUEhYQ2hwM1lRZHRWMTItNkQtLTI4M2Ffak9wWVlRTnc1Yko3bUF1T1N0T0o3cU8wRFRVWVF6czJCT1FKa0JSdHhBV2FQUnVXREN3aUNTTXZJREk0VXN4X1NwYTg5Z2hmMmdDalFjdWM1SlhBWlA?oc=5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46113.36076388889</v>
+        <v>46113.57357638889</v>
       </c>
     </row>
     <row r="39">
@@ -2525,22 +2525,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Un homme interpellé après avoir brandi un couteau à l’hôtel de ville de Roulers - 7sur7.be</t>
+          <t>"Un logement contre du sexe": un sans-papiers condamné pour avoir agressé un septuagénaire de Schaerbeek - BruxellesToday</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A man arrested after brandishing a knife at Roeselare town hall - 7sur7.be</t>
+          <t>“Housing for sex”: an undocumented migrant sentenced for attacking a septuagenarian from Schaerbeek - BruxellesToday</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 13:43:00 GMT</t>
+          <t>Wed, 01 Apr 2026 12:15:48 GMT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxNU2pFbW9GNTFZMlppRXJ5QkE0bE9mTEYwRWhnbVpUZVNtVVh3ZUtsR0tYQWtYYkx0cHg5R2J2d1g1QnpsalZZeFhHeDd1YTJBYkZHSDdEaW9Mcl9veko3cE5wMjZfVFJqWm5XOGtPTFVZMV80LTJsYXpyQVdSc09SNEwycFRFZG1CMTFPMlFObkduODNDbDdBdWR0YlJwOV9uMFhtR0pQMjJ0b3NxOU1HV1hUTW9FRHRzcWZfdUVqSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQZFNycEpwZElrblZFQzNoM3NEb1JETDc5VEVOUnM3V3gxZnR2NXotSG5NNkxjM2NwcHFBRUdjSmszS1BHdTBJcENNSTJPVWVVSndqQkRPTTdIWllCQ0dyREtwOG44bDJhcEFYSlFZdUlRRFgtUnhZZzgwV3ZJaV8zel9BRkVzcDQ4RUZv?oc=5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46113.57152777778</v>
+        <v>46113.51097222222</v>
       </c>
     </row>
     <row r="40">
@@ -2635,22 +2635,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>"Un logement contre du sexe": un sans-papiers condamné pour avoir agressé un septuagénaire de Schaerbeek - BruxellesToday</t>
+          <t>Immigration: quand Trump inspire les européens sur les expulsions de migrants - lanouvelletribune.info</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>“Housing for sex”: an undocumented migrant sentenced for attacking a septuagenarian from Schaerbeek - BruxellesToday</t>
+          <t>Immigration: when Trump inspires Europeans on expulsions of migrants - lanouvelletribune.info</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 12:15:48 GMT</t>
+          <t>Wed, 01 Apr 2026 14:22:26 GMT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxQZFNycEpwZElrblZFQzNoM3NEb1JETDc5VEVOUnM3V3gxZnR2NXotSG5NNkxjM2NwcHFBRUdjSmszS1BHdTBJcENNSTJPVWVVSndqQkRPTTdIWllCQ0dyREtwOG44bDJhcEFYSlFZdUlRRFgtUnhZZzgwV3ZJaV8zel9BRkVzcDQ4RUZv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNNm04bThRcktoTWwxOF9VcjNHMjc2WmFlWnJIaThILWM1dXk1OUc2cDFjMURaVDhuVmsySEdRMHptQWZ5SUZ2R1ZTZUdrSDMxVjBNbnV5TlhlQm1OOWNQcWRWTG5pMDJHMV9YRThmNGphdWtVVFdoRlJsSFhTajVFTVF4d01xWUllaFFSWWI3MS1CZ18tQm5xQUo3RnVPM1NaeGs4a3dkc25CTElmWWlKMDdmMTdpWjA?oc=5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2674,38 +2674,38 @@
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46113.51097222222</v>
+        <v>46113.59891203704</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Local Town Maasmechelen Dutch</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Grève spontanée des chauffeurs de bus dans un important dépôt à Mortsel : la région d'Anvers impactée - VRT</t>
+          <t>“Ik sprak de politie zelf aan, en werd toen gecontroleerd”: functionaris aan het Europees hof van Justitie betrapt met te veel alcohol na Pukkelpop | Foto - HLN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Spontaneous strike by bus drivers in a major depot in Mortsel: the Antwerp region impacted - VRT</t>
+          <t>“I spoke to the police myself, and was then checked”: official at the European Court of Justice caught with too much alcohol after Pukkelpop | Photo - HLN</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 12:14:01 GMT</t>
+          <t>Wed, 01 Apr 2026 20:28:22 GMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQRG1DcDRkTkRnTE54ZG45SWVoNVltZVp4bW4zOWt2YndrTjZUVksyNDk1d2ZnbmhWaVNpM1BKcE1zZVlybVgwOXVKaW5HNnh5T0xYTFJBbUNKZFI5dkstSEhwQ1loRG9odDBZWGs2NktSOEdIYUNjZlFNNEhIZGNfMVA2c3JyTGdHLWE4NkhmT0lOZks5N24yaDJIV3ZLeWZkamlpdmU2aw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgJBVV95cUxQcWNDV0I2WkJBRGpkZFZfN1NJaTc2YmRFWVd5dUMxTUtmdEptWHBZcmZLaWx0akpjSE5Takxrd244Wi1MLWtkcjZaNVpCZkZza1k0emxhV2E2V1ZaNnVDS3djLW1PTjNhaU1yWXFjQmIxXzlCaXZfNVFjLU5JcDRQdTFXRksyVGUxRXRpS1VIUGFlYk1LQUhtLWw0VXdYU096blViY05zOWUtR05nTnFXOUpRX0NOT3oybmIyOXZwcU1NMkVBT1U2Q1ZWQ2VyTVNpX0N1N1lERUxxMFpVLWt2R25KalpkUUVzYmNRRFNMajJIekZ5MFM5Z3ZDMU5tNGhGZzh6by1Rc3N1d2N3T08taFBQUWVYQnhYUFE?oc=5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2725,42 +2725,42 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46113.50973379629</v>
+        <v>46113.85303240741</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Local Town Maasmechelen French</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Immigration: quand Trump inspire les européens sur les expulsions de migrants - lanouvelletribune.info</t>
+          <t>Pour Bally Bagayoko, maire de Saint-Denis, il faut fermer CNews - France 24</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Immigration: when Trump inspires Europeans on expulsions of migrants - lanouvelletribune.info</t>
+          <t>Pour Bally Bagayoko, maire de Saint-Denis, il faut fermer CNews - France 24</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 14:22:26 GMT</t>
+          <t>Wed, 01 Apr 2026 17:43:13 GMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNNm04bThRcktoTWwxOF9VcjNHMjc2WmFlWnJIaThILWM1dXk1OUc2cDFjMURaVDhuVmsySEdRMHptQWZ5SUZ2R1ZTZUdrSDMxVjBNbnV5TlhlQm1OOWNQcWRWTG5pMDJHMV9YRThmNGphdWtVVFdoRlJsSFhTajVFTVF4d01xWUllaFFSWWI3MS1CZ18tQm5xQUo3RnVPM1NaeGs4a3dkc25CTElmWWlKMDdmMTdpWjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQR3N0ekFHbW9takJET3R3eEVCMVFSd3ppWUo2bTRmeXVTZHQwVW4tX0YyYVlfRFkwOVdnTjh3NlZWNkFHQWpUU2ZqOHZ1cFRpQmtBSEU4T2FPTGRJVU9nWWk1bmVDazdOalNPTmhxY1BsbnlPb3I5bC1ROUVMdkFOelRGQnZmdXQxWjRHeVNnaDdVQ2tQTHVuT0Z1ZjYxN1d2aWxmQ1oybU5uUG81UHF0NXNFMEM?oc=5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2784,38 +2784,38 @@
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46113.59891203704</v>
+        <v>46113.7383449074</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Local Town Maasmechelen French</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TC Bruxelles - Un expert désigné dans un dossier d'agression à l'encontre d'un contrôleur et de policiers - MSN</t>
+          <t>Injures discriminatoires et cyberharcèlement aggravé : Booba sèche une nouvelle fois son procès - Libération</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TC Brussels - An expert appointed in a case of assault against a controller and police officers - MSN</t>
+          <t>Discriminatory insults and aggravated cyberharassment: Booba once again skips his trial - Libération</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 13:45:57 GMT</t>
+          <t>Wed, 01 Apr 2026 14:17:09 GMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAJBVV95cUxPbWo3MW5iY0RkRVBURXJnVU5uRmo1M0ZqZHU4U3g1VG1BV0JmZ1dDNElKVnJPWmtsSzNJS3B3WFhJNktXSHMxbzVXTGlBbWlqaEk2bzBfOEpveFctZmI2b0ZGZzB1N3ZVdjU0blRfLWNkWEJwNWk4MGpycnF3MV9KQmdETWNCN3k1VFdvN0I2NTlMdWlVU2JaaE5iUEhYQ2hwM1lRZHRWMTItNkQtLTI4M2Ffak9wWVlRTnc1Yko3bUF1T1N0T0o3cU8wRFRVWVF6czJCT1FKa0JSdHhBV2FQUnVXREN3aUNTTXZJREk0VXN4X1NwYTg5Z2hmMmdDalFjdWM1SlhBWlA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNQ3k0bVJJalhUV3NoVzdLUnh6MlZLdjdLdkRHcnFmSExJNk5qMEF3YmZWT3k1TmZJUzJqQlVaNkppSDVYR0UyX29sY1RKQ2tMYnNuemFkWTFFRldiMmlIb1N3OWxXTTZ0UkhJeUxVekdMYkUzY19OMkNudDNtanhZZzA1eXdfUDZiSUFFbWhGQWZ1SVNzSHc0Sk90LWtrZ3JhWEtrejFMU2tPaDdIaXMtSzY0cFNLaENwWTFrZUY2eGNOVE1BYXFsVndHN0lFUU8wajdQUm9NWGZfNm5XV0ZlRlNJYXh0alVzZ3l2MjNWV0JnbjY1dHp3aGRoTEcwNVhvOWFvd2RmUEQwSDA?oc=5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2839,38 +2839,38 @@
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46113.57357638889</v>
+        <v>46113.59524305556</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Local Town Maasmechelen French</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>La SNCB veut inciter les Belges à prendre le train avec la carte Train+ - 7sur7.be</t>
+          <t>«Honte à vous !», «larbin»... Emmanuel Macron salue la chute de Maduro, les Insoumis enragent - lejdd.fr</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SNCB wants to encourage Belgians to take the train with the Train+ card - 7sur7.be</t>
+          <t>“Shame on you!”, “stooge”... Emmanuel Macron welcomes the fall of Maduro, the rebels are enraged - lejdd.fr</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 14:14:00 GMT</t>
+          <t>Thu, 02 Apr 2026 03:53:47 GMT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOY2F5WkU5STVlQzVXS004RHM0RldudlYwQlhyRmdFaGdmSkJEWkJCQWNDeEtTVFVLQXZNalB2ejlSdWxNOGZodjhaZVdoRUZDbml4VW94LS1Mb1VwZW1oUGhxXzgxVGNDODRtY3NhQmt2ekUwZkJ2SGgzNUdGNF9YVFdaRFl5ajdjQ0ZicEJYY1Q5RDBCWnAxeXdnRmFsVjU4RnM0U1hkQkltNGYxUUk4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQYV82WWVZVUhEOU5McDBuOG5CNU5QN2hJc3FadnhjWklMSXpGX3Ftd0paNEE5Z3FzTktmZE9uQks3c0E5cEY5TFJReXVRN1BjQjJFdU93VEd2Z0ZDRFhQcXpWYXpJWFAtbmNPRTVaZXRHbGtGOE00Q09vRXFWcnlLVmpmQWFDQ1VPN2JPa05XNkI5UU1uQ3lERkdqYzYzcDF6WG9fYjBmcGlEUDRNMV80VW9ISGdVOENrMEdkMA?oc=5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2894,38 +2894,38 @@
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46113.59305555555</v>
+        <v>46114.16234953704</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>Local Town Maasmechelen English (fallback)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Le gouvernement bruxellois obtient une nouvelle ligne de crédit auprès d’ING - 7sur7.be</t>
+          <t>France's Dassault says 'weeks' left to save Europe warplane project - France 24</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>The Brussels government obtains a new credit line from ING - 7sur7.be</t>
+          <t>France's Dassault says 'weeks' left to save Europe warplane project - France 24</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 07:14:00 GMT</t>
+          <t>Wed, 01 Apr 2026 10:41:12 GMT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNU3l4YjVjb2sxLTdCVzRqZk5zU1JKeEljRHp1Tng5Tm9XbXRXS0lvWUxqLWVRcmlGWnRZOEc4SFBWSHNRU2hQQ2lIUWZVdDF4ZHM5NmUyeC1qLTJmZ0FvYWtTZUJKYXJUcUl3bV9NWEtvaWpVaDFfWGlaTmNIR0xuNTl6X3p3aWtyWTJ6Qjd1WGJXUF91dW9ZdTRZZUxGa01LbzNpWHA3VmJmbWRzVGFZOXZncC1tZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQMFJzWmdhYTJvU0xXdnhqcDIyS05RcFdfTlZrbTJuN244c0JjZkFVb0RzY0xUMDBteS16NFlNcXVwWGhhdVBmaDVzTlJhWFRNMnpnUXJLbFhESjh6Vlc0d2xwMUtkS2tQZjlGd3V3MzRGQmdDbVhBV3lLOGtmaG9KcUYxdjhXOEY5LVNHSWU5X3VHVjdad2U3RDRwak1QMGljUUU5NG16azJ5NTlDSEVwWDlB?oc=5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2935,52 +2935,52 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46113.30138888889</v>
+        <v>46113.44527777778</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen Dutch</t>
+          <t>Local Town Maasmechelen English (fallback)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Explosie bij juwelier in Heusden: dieven vluchten zonder buit, Koolmijnlaan afgesloten - VRT</t>
+          <t>The Future Combat Air System (FCAS) programme was launched in 2017 to replace the Rafale jet and the Eurofighter planes used by Germany and Spain - themercury.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Explosion at jeweler in Heusden: thieves flee without loot, Koolmijnlaan closed - VRT</t>
+          <t>The Future Combat Air System (FCAS) programme was launched in 2017 to replace the Rafale jet and the Eurofighter planes used by Germany and Spain - themercury.com</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 06:54:24 GMT</t>
+          <t>Wed, 01 Apr 2026 11:03:07 GMT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxOUldLU3o3WlBKSC1RUmpwRVRPdjc2aDBnYnpXTDUzUEVqRGtLSjBLUERwWk1HckVNeUR4SmEzRzNWMlBwcHp4WGx4WEVWUnFyM2V3cl80VzJuY3k3U0s4T3l5bHdkWFVDZmNremlTMDI2UXE3OFBoMFI0bGszdUlZSUM4RlcyOVRp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNUHIwT1A4VXdhYS1vbzRBMThIR1Fnd0I1M3E2RWYtb2h0LUE0V3AxclNReFY0a0RuTndzOHRydFp6VXJhb3FoRmVhVWZsRmdnR2p1RVZQZk51YzU3dW92X2psZFJJZklhcWJnUS1hci1jYjBOdjhURzVkT2tTWHpINThBeHRsRS1YeDh0OFlENjBmRDNkOUFWNHlheUdQWGNkaHlsZXc4Qm13Um5vV1hXa0lrSWtoclFHRjRRcHkyYUN5SVBaclliVlIzNTNfWHQ1NXpBZE5vUmdTT3J5cW9kZDBzMjFGZG1uY2t5UHc0Mzg4OXZnRFRhYUN3TmFuOWll?oc=5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2990,52 +2990,52 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46114.28777777778</v>
+        <v>46113.46049768518</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French</t>
+          <t>Local Town Maasmechelen English (fallback)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pour Bally Bagayoko, maire de Saint-Denis, il faut fermer CNews - France 24</t>
+          <t>Boeing gets Pentagon deal to triple Patriot missile seeker output - qz.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Pour Bally Bagayoko, maire de Saint-Denis, il faut fermer CNews - France 24</t>
+          <t>Boeing gets Pentagon deal to triple Patriot missile seeker output - qz.com</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:43:13 GMT</t>
+          <t>Wed, 01 Apr 2026 16:21:03 GMT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQR3N0ekFHbW9takJET3R3eEVCMVFSd3ppWUo2bTRmeXVTZHQwVW4tX0YyYVlfRFkwOVdnTjh3NlZWNkFHQWpUU2ZqOHZ1cFRpQmtBSEU4T2FPTGRJVU9nWWk1bmVDazdOalNPTmhxY1BsbnlPb3I5bC1ROUVMdkFOelRGQnZmdXQxWjRHeVNnaDdVQ2tQTHVuT0Z1ZjYxN1d2aWxmQ1oybU5uUG81UHF0NXNFMEM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE5GRU94YUpiSE5jSnNIZm54Tkl1X3huY2xJTXZMczhDaDFNRG5OTzY4VmZEMk1mMGpaNEdJWmpuZEEtTUpoWG9zU1IyOERHNjZ2OTBybDBsV2tTWExLZDdfWA?oc=5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3045,52 +3045,52 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46113.7383449074</v>
+        <v>46113.68128472222</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Injures discriminatoires et cyberharcèlement aggravé : Booba sèche une nouvelle fois son procès - Libération</t>
+          <t>Miami-Dade and Broward County Medical Associations Announce Winners of Medical Students and Residents Research Competition - Florida Hospital News and Healthcare Report</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Discriminatory insults and aggravated cyberharassment: Booba once again skips his trial - Libération</t>
+          <t>Miami-Dade and Broward County Medical Associations Announce Winners of Medical Students and Residents Research Competition - Florida Hospital News and Healthcare Report</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 14:17:09 GMT</t>
+          <t>Wed, 01 Apr 2026 20:24:39 GMT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxNQ3k0bVJJalhUV3NoVzdLUnh6MlZLdjdLdkRHcnFmSExJNk5qMEF3YmZWT3k1TmZJUzJqQlVaNkppSDVYR0UyX29sY1RKQ2tMYnNuemFkWTFFRldiMmlIb1N3OWxXTTZ0UkhJeUxVekdMYkUzY19OMkNudDNtanhZZzA1eXdfUDZiSUFFbWhGQWZ1SVNzSHc0Sk90LWtrZ3JhWEtrejFMU2tPaDdIaXMtSzY0cFNLaENwWTFrZUY2eGNOVE1BYXFsVndHN0lFUU8wajdQUm9NWGZfNm5XV0ZlRlNJYXh0alVzZ3l2MjNWV0JnbjY1dHp3aGRoTEcwNVhvOWFvd2RmUEQwSDA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNN0lMNF9IQ2J0OUFNdmszRHJrZWRlYjVIazJkck9OSFpYTFRjQUhMMXRydDZLRDJXU0wyQlFLQnhRUGUxTFpxa2lwTGlLdjFUamtQMFRoTVpSOFdLQkdHS25uZ2FHM3d6SW1rVF9meEcyRXBoRWwyb21sc2lmVnBDdHducHRvN09NV1RhSC04bGFQclFRSFJ5Q2FPZnlMYVlZQWVKR1M1NGpSek14cmxUazkybERBSkpJX0l4WFJhT3IyWTVRMFdoZ3JJV3FoTUU4ZmFKc1JZc1o0MUstMVBBWll2N1Q4VVo4NG5CS3FjNTBiZVcy?oc=5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3100,52 +3100,52 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46113.59524305556</v>
+        <v>46113.85045138889</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French</t>
+          <t>Local Town Ingolstadt German</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
+          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>«Honte à vous !», «larbin»... Emmanuel Macron salue la chute de Maduro, les Insoumis enragent - lejdd.fr</t>
+          <t>Polizisten in unüblicher Rolle – Nächtlicher Vorfall an einer Bushaltestelle beschäftigt Ermittler - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>“Shame on you!”, “stooge”... Emmanuel Macron welcomes the fall of Maduro, the rebels are enraged - lejdd.fr</t>
+          <t>Police officers in an unusual role – a night-time incident at a bus stop concerns investigators - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 03:53:47 GMT</t>
+          <t>Thu, 02 Apr 2026 04:07:31 GMT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxQYV82WWVZVUhEOU5McDBuOG5CNU5QN2hJc3FadnhjWklMSXpGX3Ftd0paNEE5Z3FzTktmZE9uQks3c0E5cEY5TFJReXVRN1BjQjJFdU93VEd2Z0ZDRFhQcXpWYXpJWFAtbmNPRTVaZXRHbGtGOE00Q09vRXFWcnlLVmpmQWFDQ1VPN2JPa05XNkI5UU1uQ3lERkdqYzYzcDF6WG9fYjBmcGlEUDRNMV80VW9ISGdVOENrMEdkMA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQcFdzMW1iQ1N5VGJ0dnk0TXhSN0JCRV9obDhiYl8tQ2xISlp6cGw3UEs2UG85RG1kdmRFbHhISmRfSEVrYnc1bzJUa1VkT25mZjI0Q1lsaWVJcFYwQk15NTMzMndvMmU5Y210VDNQbld3dF9vRUZtb1Qyb29teWxIcm0tb0dxVlNVd01uS3ppVUZMSk9OZ1JxRU52UktnQzNBaDNzSmpLMlE2UFQySUxldE9YRWp4S0g5aC1GYlh2dVBVQQ?oc=5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3155,52 +3155,52 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46114.16234953704</v>
+        <v>46114.17188657408</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen English (fallback)</t>
+          <t>Local Town Ingolstadt German</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France's Dassault says 'weeks' left to save Europe warplane project - France 24</t>
+          <t>Zimmer brennt: Polizei ermittelt - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>France's Dassault says 'weeks' left to save Europe warplane project - France 24</t>
+          <t>Room is on fire: Police investigate - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 10:41:12 GMT</t>
+          <t>Wed, 01 Apr 2026 12:13:32 GMT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxQMFJzWmdhYTJvU0xXdnhqcDIyS05RcFdfTlZrbTJuN244c0JjZkFVb0RzY0xUMDBteS16NFlNcXVwWGhhdVBmaDVzTlJhWFRNMnpnUXJLbFhESjh6Vlc0d2xwMUtkS2tQZjlGd3V3MzRGQmdDbVhBV3lLOGtmaG9KcUYxdjhXOEY5LVNHSWU5X3VHVjdad2U3RDRwak1QMGljUUU5NG16azJ5NTlDSEVwWDlB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQMm5YYUc0SDF0VExNVUx0SVlneTZnZWQ1bHNKdkZjRkNKYy1jYXNNUVVKeVJZa2FzR1pmUUU4M1phWFJpdXRKUmlrTVA0bFYtRjc1dkFZRmd6M25zRmd4VDZtMXVIU2tKQlU5UEMxYVN2Ry1rMHBHblFiQm1sWEZ5ekZpWXhLUjZRcXplMzVzRlNBLVNiU0g3cnFEUmZ6Zw?oc=5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3210,52 +3210,52 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46113.44527777778</v>
+        <v>46113.50939814815</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen English (fallback)</t>
+          <t>Village Ingolstadt (fallback)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>The Future Combat Air System (FCAS) programme was launched in 2017 to replace the Rafale jet and the Eurofighter planes used by Germany and Spain - themercury.com</t>
+          <t>Ingolstadt vs. Muenchen Odds &amp; Predictions (Apr. 2, 2026) - Polymarket</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>The Future Combat Air System (FCAS) programme was launched in 2017 to replace the Rafale jet and the Eurofighter planes used by Germany and Spain - themercury.com</t>
+          <t>Ingolstadt vs. Muenchen Odds &amp; Predictions (Apr. 2, 2026) - Polymarket</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 11:03:07 GMT</t>
+          <t>Thu, 02 Apr 2026 00:42:13 GMT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAJBVV95cUxNUHIwT1A4VXdhYS1vbzRBMThIR1Fnd0I1M3E2RWYtb2h0LUE0V3AxclNReFY0a0RuTndzOHRydFp6VXJhb3FoRmVhVWZsRmdnR2p1RVZQZk51YzU3dW92X2psZFJJZklhcWJnUS1hci1jYjBOdjhURzVkT2tTWHpINThBeHRsRS1YeDh0OFlENjBmRDNkOUFWNHlheUdQWGNkaHlsZXc4Qm13Um5vV1hXa0lrSWtoclFHRjRRcHkyYUN5SVBaclliVlIzNTNfWHQ1NXpBZE5vUmdTT3J5cW9kZDBzMjFGZG1uY2t5UHc0Mzg4OXZnRFRhYUN3TmFuOWll?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9WUE5xX2lnd3V5ckRoZWJ2ci02ckV3UWxPbXI5M2VJcl9DMXVrNGFzTDJhZzUzVTVhckpfVmRpakJoTVppTmRtbFF0MW90eDFwNnBnLUJxTk9QMUs1c2ZTMHd3NndNbnFDd0E?oc=5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3279,38 +3279,38 @@
         </is>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46113.46049768518</v>
+        <v>46114.02931712963</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen English (fallback)</t>
+          <t>Village Ingolstadt (fallback)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boeing gets Pentagon deal to triple Patriot missile seeker output - qz.com</t>
+          <t>Audi's Five-Cylinder Engine Will Live On Outside Europe - inkl</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Boeing gets Pentagon deal to triple Patriot missile seeker output - qz.com</t>
+          <t>Audi's Five-Cylinder Engine Will Live On Outside Europe - inkl</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 16:21:03 GMT</t>
+          <t>Thu, 02 Apr 2026 07:23:06 GMT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE5GRU94YUpiSE5jSnNIZm54Tkl1X3huY2xJTXZMczhDaDFNRG5OTzY4VmZEMk1mMGpaNEdJWmpuZEEtTUpoWG9zU1IyOERHNjZ2OTBybDBsV2tTWExLZDdfWA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxPNy04R2NWN1RiUXh6QUFXUkN4d1RXdTgxUmx2THpLWkZBelU4MF9CRUJORmNiREM5S01hNmlzdGtocUJGNVowUU1kM1pNdTdlVWxrbjhtRnJ6cXZweXZFOU43Qmw1UXR3eTF3dEsxMmhJN1RYYzhnZjR4M2MwSjNMT0hveTluaWUt?oc=5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3334,38 +3334,38 @@
         </is>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46113.68128472222</v>
+        <v>46114.30770833333</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>Village Ingolstadt (fallback)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami-Dade and Broward County Medical Associations Announce Winners of Medical Students and Residents Research Competition - Florida Hospital News and Healthcare Report</t>
+          <t>FC Ingolstadt 04 vs. FC Erzgebirge Aue - Live Score - May 03, 2026 - foxsports.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Miami-Dade and Broward County Medical Associations Announce Winners of Medical Students and Residents Research Competition - Florida Hospital News and Healthcare Report</t>
+          <t>FC Ingolstadt 04 vs. FC Erzgebirge Aue - Live Score - May 03, 2026 - foxsports.com</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 20:24:39 GMT</t>
+          <t>Wed, 01 Apr 2026 12:07:23 GMT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxNN0lMNF9IQ2J0OUFNdmszRHJrZWRlYjVIazJkck9OSFpYTFRjQUhMMXRydDZLRDJXU0wyQlFLQnhRUGUxTFpxa2lwTGlLdjFUamtQMFRoTVpSOFdLQkdHS25uZ2FHM3d6SW1rVF9meEcyRXBoRWwyb21sc2lmVnBDdHducHRvN09NV1RhSC04bGFQclFRSFJ5Q2FPZnlMYVlZQWVKR1M1NGpSek14cmxUazkybERBSkpJX0l4WFJhT3IyWTVRMFdoZ3JJV3FoTUU4ZmFKc1JZc1o0MUstMVBBWll2N1Q4VVo4NG5CS3FjNTBiZVcy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWWJzNnFLRlpUbkZmaE56UzVZMVZaeU11dUVEVXpVMEhhNlNROURrT3NqNkVIMDNqaTdpTWtMNkRKNzVMd19vWElxMkdJc3I3Vm42WEhEWE0zNzA4azNZcTRSV0Y5c1ZET0tkMVJsWktkSXJNdVc1ZC1PTEd3aXgtRjBfTW4wMnNkUml0ZXRVUXVXUHRZbVI4ZWZXLUxwRThSNUF0OUZ3?oc=5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3389,38 +3389,38 @@
         </is>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46113.85045138889</v>
+        <v>46113.50512731481</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Local Town Ingolstadt German</t>
+          <t>Village Bicester Kildare</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
+          <t>("Bicester Village" OR "Kildare Village" OR "Bicester outlet" OR "Kildare outlet")</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Polizisten in unüblicher Rolle – Nächtlicher Vorfall an einer Bushaltestelle beschäftigt Ermittler - Augsburger Allgemeine</t>
+          <t>Kildare chef charged with 15 thefts gets chance - kildare-nationalist.ie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Police officers in an unusual role – a night-time incident at a bus stop concerns investigators - Augsburger Allgemeine</t>
+          <t>Kildare chef charged with 15 thefts gets chance - kildare-nationalist.ie</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 04:07:31 GMT</t>
+          <t>Wed, 01 Apr 2026 21:52:00 GMT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQcFdzMW1iQ1N5VGJ0dnk0TXhSN0JCRV9obDhiYl8tQ2xISlp6cGw3UEs2UG85RG1kdmRFbHhISmRfSEVrYnc1bzJUa1VkT25mZjI0Q1lsaWVJcFYwQk15NTMzMndvMmU5Y210VDNQbld3dF9vRUZtb1Qyb29teWxIcm0tb0dxVlNVd01uS3ppVUZMSk9OZ1JxRU52UktnQzNBaDNzSmpLMlE2UFQySUxldE9YRWp4S0g5aC1GYlh2dVBVQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNLVE4ZFZLNGwyX1NNdnUyaDJCV0ZadkdqWk5PdlRrdUsyc0FvMVc5TlpXbHRHVkp4ZkE2N3Y0TW5ud2pLU3RjWHdTTkZYajlTU2V2V3h5QWZoY3BkdEJ3c0JkRC1NWU1qVGhzdGtBSlZKYldWdHQ5NUtMZS1VZUp4bG56NVBlWF92Zm44REtfUU80ZWt6R0FIWURKelRUdmM?oc=5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3430,52 +3430,52 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46114.17188657408</v>
+        <v>46113.91111111111</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Local Town Ingolstadt German</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Zimmer brennt: Polizei ermittelt - Augsburger Allgemeine</t>
+          <t>2026 film and high-end TV productions shooting in the UK and Ireland: latest updates - screendaily.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Room is on fire: Police investigate - Augsburger Allgemeine</t>
+          <t>2026 film and high-end TV productions shooting in the UK and Ireland: latest updates - screendaily.com</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 12:13:32 GMT</t>
+          <t>Thu, 02 Apr 2026 07:27:50 GMT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQMm5YYUc0SDF0VExNVUx0SVlneTZnZWQ1bHNKdkZjRkNKYy1jYXNNUVVKeVJZa2FzR1pmUUU4M1phWFJpdXRKUmlrTVA0bFYtRjc1dkFZRmd6M25zRmd4VDZtMXVIU2tKQlU5UEMxYVN2Ry1rMHBHblFiQm1sWEZ5ekZpWXhLUjZRcXplMzVzRlNBLVNiU0g3cnFEUmZ6Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQZmNMRTBhWHdsbFo0WHUtenBKUWJ0Z09LVVBuTjVUb1R6dnYyV0UwSEluX01NUXJuVzhuVlZCTUlHanpOQ0hpT1p4N2xGSnIyaEg3eGRKQ3BZVlJWT0hPREU4dmd2azc2VGVhQVl2emFKVmpENnNrT3BJNGVDY2xlNDVSUV95dzdPcHFtOHhqcG9WbUdYYU9odjhUTHp2b0dzMTZ6Yzh4U1VGNVVfeVl5RmQ1eDJpLU91MHlMUS1kZlZNNng3LTE1VHNIb1o?oc=5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3485,52 +3485,52 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46113.50939814815</v>
+        <v>46114.31099537037</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Village Ingolstadt (fallback)</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ingolstadt vs. Muenchen Odds &amp; Predictions (Apr. 2, 2026) - Polymarket</t>
+          <t>Woman in her 80s stabbed to death outside her south London home - London Evening Standard</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ingolstadt vs. Muenchen Odds &amp; Predictions (Apr. 2, 2026) - Polymarket</t>
+          <t>Woman in her 80s stabbed to death outside her south London home - London Evening Standard</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 00:42:13 GMT</t>
+          <t>Thu, 02 Apr 2026 09:58:37 GMT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9WUE5xX2lnd3V5ckRoZWJ2ci02ckV3UWxPbXI5M2VJcl9DMXVrNGFzTDJhZzUzVTVhckpfVmRpakJoTVppTmRtbFF0MW90eDFwNnBnLUJxTk9QMUs1c2ZTMHd3NndNbnFDd0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPdGpsV3hOSHZWWFZCT3JCQTFHc2o3d3cwb3ZPOWlzUTBkdXN3emdCOXkzVzJMaE9DYW55RWFvQlpkLWk0WW82NEVPRmhQRWktN0JlZ2ZEaWxHQXVtZl84WmN2T081OS1HSEpON3NhY1E1bm90cDdWcVdoTUJlMm1UQ3hEY0dvUFZERUs1VzF1R2dSa1E?oc=5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3554,38 +3554,38 @@
         </is>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46114.02931712963</v>
+        <v>46114.41570601852</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Village Ingolstadt (fallback)</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>("Ingolstadt Village" OR "Ingolstadt") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FC Ingolstadt 04 vs. FC Erzgebirge Aue - Live Score - May 03, 2026 - FOX Sports</t>
+          <t>'Lovely neighbour' stabbed to death in Shooters Hill named in tribute - London Now</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FC Ingolstadt 04 vs. FC Erzgebirge Aue - Live Score - May 03, 2026 - FOX Sports</t>
+          <t>'Lovely neighbour' stabbed to death in Shooters Hill named in tribute - London Now</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 12:07:23 GMT</t>
+          <t>Thu, 02 Apr 2026 07:36:36 GMT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNWWJzNnFLRlpUbkZmaE56UzVZMVZaeU11dUVEVXpVMEhhNlNROURrT3NqNkVIMDNqaTdpTWtMNkRKNzVMd19vWElxMkdJc3I3Vm42WEhEWE0zNzA4azNZcTRSV0Y5c1ZET0tkMVJsWktkSXJNdVc1ZC1PTEd3aXgtRjBfTW4wMnNkUml0ZXRVUXVXUHRZbVI4ZWZXLUxwRThSNUF0OUZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxNVVliUFRybU1oNjhyRFNkWnl3OC1iUEtQZGxoTHRMbl9Ta2taVmxMRUVXOXA1QW1ZSFFUUXI3UzViM2ZUQ3l4MUJwLWdDZ2xKZ1NTNUpJOWJfLVM3ZVh0Zk1NX1k2djVLc290UE5oNGR6UEtJTjVGc0JiTVRmTFltR2labnA2SEhDTTZBVUNGMkRBZ2ZqXy1QSFJwOA?oc=5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3609,38 +3609,38 @@
         </is>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46113.50512731481</v>
+        <v>46114.31708333334</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Village Bicester Kildare</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>("Bicester Village" OR "Kildare Village" OR "Bicester outlet" OR "Kildare outlet")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kildare chef charged with 15 thefts gets chance - kildare-nationalist.ie</t>
+          <t>Armed police rush to shooting with in Walthamstow - Guardian Series</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Kildare chef charged with 15 thefts gets chance - kildare-nationalist.ie</t>
+          <t>Armed police rush to shooting with in Walthamstow - Guardian Series</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 21:52:00 GMT</t>
+          <t>Wed, 01 Apr 2026 16:30:33 GMT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOazZvSmVWOUw0VlJCWk5GUTA5UjBmTGVjVVBHbndTd1FDaTN5UW5ldTRtU2Frdkt1ZDJ5SlNpTWxnY3hJYXNJd0NRWW1iOUpXRVdBS3ZFM2xLSXdvOEp0M0x5T1IxM0ltakpKZkdIRlFIS3lnUi03ZmpPcEpzQ3prNXlUdWs0ZUJNZHQtcllaUmhrc01vYnVaVDV6S3Q0VHJVOThIXw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNb0ZDcXBNdFhEWERaaTE3a01BVURfR1VNeWxZM3RwdWFhRHEwOHlRb1UxTGZlNmcxMFR1WVVWTHRqYlZoUndJenRwMEZxU3FIcmc0eWxHODJyR0FKeUhCVEpBTmtCTk0zRk9IQ3lxcW9PMS00dTRzV0VxNUdrZC1TVndRdEUwZHhjeGF0WE10UnFIcEc4RHlLbC1UVk9KekZwN09J?oc=5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3664,38 +3664,38 @@
         </is>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46113.91111111111</v>
+        <v>46113.68788194445</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Village Bicester Kildare</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>("Bicester Village" OR "Kildare Village" OR "Bicester outlet" OR "Kildare outlet")</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Talks, pop ups and freebies: The best London beauty events to attend now - MSN</t>
+          <t>Lurgan proxy bomb attempt ‘would have caused devastation’, Long says - East London Advertiser</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Talks, pop ups and freebies: The best London beauty events to attend now - MSN</t>
+          <t>Lurgan proxy bomb attempt ‘would have caused devastation’, Long says - East London Advertiser</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 07:42:52 GMT</t>
+          <t>Wed, 01 Apr 2026 14:25:54 GMT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AJBVV95cUxOWkdqNGE5cVM2LWZ2U1BTeUxUU1dyckhLWW9Fa0paOG52S2tjX2N4czZzY1d4N1hvR2ZmZmRZMzRaeElIM3h3SlBBTVoxV3ltRWNvallZWnRTc1VVaVZHeVF6RHU0dkc3RmVhYnNfUHVlMkZZdTN2NUlfUlBGNVFNNnBQTzFhUEZIaWp4ZUtSbjE3dzNlS3NrNDZGb3Z1Tll0WlRDXzlCZFh4a2pFcHZnal83WG9qZWtRQjBfM281TUlKVzQ5eTlGSnV4bDJTYXpETWJPOURiXzRYa2JCU3lNSUw0OVJsdTU1czU2S2hpZWVlQ2pjemUzQTFtcXZPNS11cHBqNmRsOXFxZFB0MVNFME9kRTVFVW1SYS1mdTU5NFNJaVFzNWwtenppbjRJTGt4UGprRlVmVVdIcXNxUWRRWXhrRjVtM25ZR3ZmRVJ6cnJ1elZRYl95Tm9uY0Q?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOQlRMVmJqS2l6ZzVyNkFlVTYxUEdGVUZnOUhZdEx1eWpvWEJhTTY3UWpXREcyd21NdUVGd29jLWIzNWRnTUd1bzFHLXc3RlFtWTUwWDR0VjhCVF9ubEFibWlQUGNRdXVwZnVldUlxeXlCYUc5RWFUSzFOdUZpN0ZVcHExS2llLTcxaEV5VnZqSVFicWJfNE45ZDEyRFExWU5EN2FYbzU1ZW9jMFhZQXhETDdYM0Z3azJWOFN1WENkUGg?oc=5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46113.32143518519</v>
+        <v>46113.60131944445</v>
       </c>
     </row>
     <row r="61">
@@ -3735,22 +3735,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026 film and high-end TV productions shooting in the UK and Ireland: latest updates - Screen Daily</t>
+          <t>Kanye West gets huge snub ahead of explosive concert in London after decade - The News International</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026 film and high-end TV productions shooting in the UK and Ireland: latest updates - Screen Daily</t>
+          <t>Kanye West gets huge snub ahead of explosive concert in London after decade - The News International</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 21:41:35 GMT</t>
+          <t>Wed, 01 Apr 2026 18:56:00 GMT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxQZmNMRTBhWHdsbFo0WHUtenBKUWJ0Z09LVVBuTjVUb1R6dnYyV0UwSEluX01NUXJuVzhuVlZCTUlHanpOQ0hpT1p4N2xGSnIyaEg3eGRKQ3BZVlJWT0hPREU4dmd2azc2VGVhQVl2emFKVmpENnNrT3BJNGVDY2xlNDVSUV95dzdPcHFtOHhqcG9WbUdYYU9odjhUTHp2b0dzMTZ6Yzh4U1VGNVVfeVl5RmQ1eDJpLU91MHlMUS1kZlZNNng3LTE1VHNIb1o?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQYTJXdHYxdURLWGVfc09YdU43R1VINWJGSUtOVGl3Sjk5MVEwQVRBTXRBR3hkODVKbjUxUE9CLVJuSjlZY292enNmWDNTeTZWY3dLMkY4cXJlblN6Zm0xMnYybU40NGdSenkyY1dqUnhDcTJ4RFRYLUVCU2VreEh5ZGlqM1UwSWtnTGZpZWNBVVdsdnlWOUJUa3VpTEJvWGY4UFdYSVpEUjVNUdIBpgFBVV95cUxNTHAwR2tKd3dZS2twblg0UVFyVGl0OGppWG9DTDBkTURFNDhGZC05SEN1QnZGNThkeUtMcUFMSG56cU91S2FEUE5ITXcxeTh4cFRGak9lOERfbFRvNkVtN1loRGh2SG5aRDF4cXNrbW96bi1rQjR6TkktVVNYSUdtVHZKeFhYQTBHTFNPSUE0TWt5dkZIeDhybXB0aEdqRXpCUE1SX2hn?oc=5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="K61" s="1" t="n">
-        <v>46113.90387731481</v>
+        <v>46113.78888888889</v>
       </c>
     </row>
     <row r="62">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Woman in her 80s stabbed to death outside her south London home - London Evening Standard</t>
+          <t>LIVE updates as police investigate day after woman killed in Shooters Hill - London Now</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Woman in her 80s stabbed to death outside her south London home - London Evening Standard</t>
+          <t>LIVE updates as police investigate day after woman killed in Shooters Hill - London Now</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 01:37:35 GMT</t>
+          <t>Thu, 02 Apr 2026 06:35:34 GMT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPdGpsV3hOSHZWWFZCT3JCQTFHc2o3d3cwb3ZPOWlzUTBkdXN3emdCOXkzVzJMaE9DYW55RWFvQlpkLWk0WW82NEVPRmhQRWktN0JlZ2ZEaWxHQXVtZl84WmN2T081OS1HSEpON3NhY1E1bm90cDdWcVdoTUJlMm1UQ3hEY0dvUFZERUs1VzF1R2dSa1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPclh6Ni1nckppUmlLSW90dHRfNU5TT3ZOQ3dXWWcxOUNuTnd6N2IwRF92ZUJDdkJuRFQ3UklkcUFyd1JubVNVV0EwNTFMbkR5VzVXNV9HeEZFQVJjS0VraU9OR2tJanFnaEZLTDBQYTAtVV9UNEYzYk5GU2ZjVG85Q3NCbEMyNzZOR0FqU0luc09HMGdMaEVTLTRYNVNsUQ?oc=5</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46114.06776620371</v>
+        <v>46114.27469907407</v>
       </c>
     </row>
     <row r="63">
@@ -3845,22 +3845,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Armed police rush to shooting with in Walthamstow - Guardian Series</t>
+          <t>Extra police patrols in Shooters Hill after woman in her 80s fatally stabbed - London Now</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Armed police rush to shooting with in Walthamstow - Guardian Series</t>
+          <t>Extra police patrols in Shooters Hill after woman in her 80s fatally stabbed - London Now</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 16:30:33 GMT</t>
+          <t>Wed, 01 Apr 2026 17:07:37 GMT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNb0ZDcXBNdFhEWERaaTE3a01BVURfR1VNeWxZM3RwdWFhRHEwOHlRb1UxTGZlNmcxMFR1WVVWTHRqYlZoUndJenRwMEZxU3FIcmc0eWxHODJyR0FKeUhCVEpBTmtCTk0zRk9IQ3lxcW9PMS00dTRzV0VxNUdrZC1TVndRdEUwZHhjeGF0WE10UnFIcEc4RHlLbC1UVk9KekZwN09J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxNTTJsVjdMVTF0dEQyTmtfQ0lFUEFkaGR6LWtzV212cEQ2WEo1b2RNY0JiSVdQbVAwbWV3c0oyX3J3Vm5nd1NCMjVxSmd2OEZpQ2tKc3F4R3lYdWRhLUZrV18xTUhxQ3BBem5QMi1sbmdMeHBsOWZybmJhNHdxNlhMc3dPY1lfSjZycjBsMUlyTnhoWWMtSHBjUXZHQThfbGs?oc=5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46113.68788194445</v>
+        <v>46113.71362268519</v>
       </c>
     </row>
     <row r="64">
@@ -3900,22 +3900,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lurgan proxy bomb attempt ‘would have caused devastation’, Long says - East London Advertiser</t>
+          <t>Man killed as three shootings shake London in days before Easter bank holiday - London Now</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Lurgan proxy bomb attempt ‘would have caused devastation’, Long says - East London Advertiser</t>
+          <t>Man killed as three shootings shake London in days before Easter bank holiday - London Now</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 14:25:54 GMT</t>
+          <t>Thu, 02 Apr 2026 09:31:38 GMT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOQlRMVmJqS2l6ZzVyNkFlVTYxUEdGVUZnOUhZdEx1eWpvWEJhTTY3UWpXREcyd21NdUVGd29jLWIzNWRnTUd1bzFHLXc3RlFtWTUwWDR0VjhCVF9ubEFibWlQUGNRdXVwZnVldUlxeXlCYUc5RWFUSzFOdUZpN0ZVcHExS2llLTcxaEV5VnZqSVFicWJfNE45ZDEyRFExWU5EN2FYbzU1ZW9jMFhZQXhETDdYM0Z3azJWOFN1WENkUGg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNNEktZTZ1Q2xISFRyd3YyVzFGMG9QeUdwLWxVV0FJSHI1X0VkOEh4VndWQlFTSGF2N3hFUVZHM0RzRDNJbHZTSDluRXJaaXVCaFoybmtvUVdMaE0wYnJCYTNxdDd3aVlULUlKdVVrVTMzZTduQWwyRUFaOENETDk2R05mcFBKdnphdW1FT2trTFRyZw?oc=5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46113.60131944445</v>
+        <v>46114.39696759259</v>
       </c>
     </row>
     <row r="65">
@@ -3955,22 +3955,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kanye West gets huge snub ahead of explosive concert in London after decade - The News International</t>
+          <t>Oil price rises as Trump warns he'll bomb Iran 'back to Stone Ages' - London Evening Standard</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kanye West gets huge snub ahead of explosive concert in London after decade - The News International</t>
+          <t>Oil price rises as Trump warns he'll bomb Iran 'back to Stone Ages' - London Evening Standard</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 18:56:00 GMT</t>
+          <t>Thu, 02 Apr 2026 06:08:21 GMT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQYTJXdHYxdURLWGVfc09YdU43R1VINWJGSUtOVGl3Sjk5MVEwQVRBTXRBR3hkODVKbjUxUE9CLVJuSjlZY292enNmWDNTeTZWY3dLMkY4cXJlblN6Zm0xMnYybU40NGdSenkyY1dqUnhDcTJ4RFRYLUVCU2VreEh5ZGlqM1UwSWtnTGZpZWNBVVdsdnlWOUJUa3VpTEJvWGY4UFdYSVpEUjVNUdIBpgFBVV95cUxNTHAwR2tKd3dZS2twblg0UVFyVGl0OGppWG9DTDBkTURFNDhGZC05SEN1QnZGNThkeUtMcUFMSG56cU91S2FEUE5ITXcxeTh4cFRGak9lOERfbFRvNkVtN1loRGh2SG5aRDF4cXNrbW96bi1rQjR6TkktVVNYSUdtVHZKeFhYQTBHTFNPSUE0TWt5dkZIeDhybXB0aEdqRXpCUE1SX2hn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxQTm5sdDNobUlybS0xLXRvTzFCQVFEcjVCb3Ezb2ZreHY1ZjNieTlBMjdNdE5GbzMzNjBnSVRvU0RkZHZhRHp5a3N0WFF4Q1BLR1FFX29NcGNCd1FkSDI5Qi1aTDJNWUJuX3puUWZhM0ZfUURFalVlRFcxT1NUdTVvTGNjckJyTGgxbEszelU2cmd5a3RIbFJ0UWdMWQ?oc=5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3994,7 +3994,7 @@
         </is>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46113.78888888889</v>
+        <v>46114.25579861111</v>
       </c>
     </row>
     <row r="66">
@@ -4010,22 +4010,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Pictured: 'Funny' and 'honest' man shot dead in car outside Euston station - London Evening Standard</t>
+          <t>What we know (so far) about the people accused in London, Ont., bomb-making scheme - MSN</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Pictured: 'Funny' and 'honest' man shot dead in car outside Euston station - London Evening Standard</t>
+          <t>What we know (so far) about the people accused in London, Ont., bomb-making scheme - MSN</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 12:44:10 GMT</t>
+          <t>Wed, 01 Apr 2026 18:50:46 GMT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNZGZ5ZTBINWRGbmZjbWU1YlhxN1dWMmVCVTRKazFWYkd1eGR3Nzc0NGMzb3FsRHdDbWRMTzdrYmZpSlJyMTFQQkE0ZzFVWUxWLWpNZVVBM3htajdrc1QxOHIxUHZwUjhfRDNDTjhBb2ItWHViOGF2amxiQXZRNHNTSDAyMXpVaUFrNDdtNHlJa0ljb3BMbjdCTGpXbTVqcEZ2RVFaOFp6dGV2NFNYRHpQZmZlVWQ5LVhG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogNBVV95cUxOanVQTzY4ekU4UG1XQzAyRV9KQmt1RHFPOVo1Zm0wc215WmQtMF94eXlURE8tM2huMTgybzJ1dFktUjJWZlMyak14S0tEUTNBdHB5d1J3eDduTVRsVm1QaWN5c1N6WnR4TFJQUF9SUGF0WUV0VUtsTHoySTRGQk9IaXVDc0s0STh0UzVZbndvMmN3bDhXaEFTd3gwNjBNdjM3cDJLMjV3YUlqT1preDRDUVlPcjlKUGpxazZSaWsydEpIQmZUMGgwX2ZOR2dQQjlEbkVqLW1WUzhVV2F3R0MxbERJeGhZTGVib3M3TGFySnNaLVNlWG5BREU5aDFpbk1JRG11Q0s5Nzc3Qi1QdnlsOE5LRE9SOGZKYjVZdUFkN0ZuOUYzV1FOYkU2bzEwc0pvREtyZE84cnZnTWZiQzZMTGZlVGRiNmJkZGRrZzdBMnlvM1l5OXR5Vm1DZFpfRHdKMVd2RTlzTnRFX1h6R2NHRzZHaTlXbl9ydndpRUI0NERSejZfRTBTRkxQVHpxQWFyNGstb19KakNiTHk2eWpuQk1B?oc=5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4049,7 +4049,7 @@
         </is>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46113.5306712963</v>
+        <v>46113.78525462963</v>
       </c>
     </row>
     <row r="67">
@@ -4065,22 +4065,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Police shut multiple roads after ‘shooting’ - london-now.co.uk</t>
+          <t>Woman (63) charged with murder after Dublin house party stabbing ‘too unwell’ to attend hearing - Sunday World</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Police shut multiple roads after ‘shooting’ - london-now.co.uk</t>
+          <t>Woman (63) charged with murder after Dublin house party stabbing ‘too unwell’ to attend hearing - Sunday World</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 09:20:20 GMT</t>
+          <t>Wed, 01 Apr 2026 16:48:00 GMT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOejFzcl9UVEREaGk2US0yczB0OFlrMHF3ZnFfa0Vjd01Fc2JFSFZ1VW5UZ2ZCLXZVTF9KaHBuelFvNHBZeWkzcE5nTjBKYnNXMWhmcTFBN2NfeS1oMk1wbnQ0UXRncVZzbVRNUlFzNkU3TzdMdnRLSjNhTzNPZHppMThpZUhPazNWYThSWktpSmtrWXZq?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQOEU2dEVBcnVUbTVTMkRkR0pDeElOYzRIek1nM2dqRWpRd0FEeDJXaVZFci1LbVZndG1IUDJfcTlVelN6a2FfYXRKVy1RaWt0S1pLV3NvQ0RuTy01eUE0UDlQYmJzV0hJSHVBOWtsRnVydkxHTmF2eDZNVFBRdWl5V1JMTHROWExCVFZKVXkzNXV1azVNVWdfalpRM0VjWnd3d1RiRDBaWkZZUGQ4cVV3dVdEWDFhbjVQTTJoOGNrY3V4dVQ3YVI3X2NRT0xtNEVpR0NhM0ZvWXBKUQ?oc=5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46113.38912037037</v>
+        <v>46113.7</v>
       </c>
     </row>
     <row r="68">
@@ -4120,22 +4120,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Man, 18, charged with murder after stabbing near Westminster Abbey - london-now.co.uk</t>
+          <t>Tributes paid to 26-year-old Nahom Medhanie after fatal shooting in Camden | News - Greatest Hits Radio (London) - Rayo</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Man, 18, charged with murder after stabbing near Westminster Abbey - london-now.co.uk</t>
+          <t>Tributes paid to 26-year-old Nahom Medhanie after fatal shooting in Camden | News - Greatest Hits Radio (London) - Rayo</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 07:47:40 GMT</t>
+          <t>Wed, 01 Apr 2026 13:42:01 GMT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNTS1lVHJYV0k1ZldkZmM3dk5qU0xyd2dfQTNra3dYMmM4N2t1UllndFJRc0FiaTZVbUluZG1uQTEtQnV1Q255bzgxNkkxdXNjaE9WVTlSaGJudnRVTTJndGNEb1ZoOWV1bEFQU0pmN0xTWGZUQUIxNUUyZFhlN3hmbkF6elVnRXVvMEdvZVZ1OXlzeFZ2dGFCTEdJd0ctcWtp?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQTWRKX09FR3lTT3pqZ3pMT0NmbnluMDVCcGVqVDZvSW00UFRhalotUmhQajdfWlFWOF9GWURDdDJFZ1BHRXlQRXlNYWVXZGFoTXJLNmZjTVA0UndOckhxUEZkbnNqck5sQkhsTDlwdFZ4SWlCbWN3ekVxTmo3RVlYSG1LSHRnWURtNFRvMFF0QkVGTXJaTzh4Q1Uwb01wTUE?oc=5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46113.32476851852</v>
+        <v>46113.57084490741</v>
       </c>
     </row>
     <row r="69">
@@ -4175,22 +4175,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>What we know (so far) about the people accused in London, Ont., bomb-making scheme - MSN</t>
+          <t>Hotel migrant faces jail after staging MI5 bomb hoax over failed asylum claim - GB News</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>What we know (so far) about the people accused in London, Ont., bomb-making scheme - MSN</t>
+          <t>Hotel migrant faces jail after staging MI5 bomb hoax over failed asylum claim - GB News</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 18:50:46 GMT</t>
+          <t>Wed, 01 Apr 2026 20:32:06 GMT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogNBVV95cUxOanVQTzY4ekU4UG1XQzAyRV9KQmt1RHFPOVo1Zm0wc215WmQtMF94eXlURE8tM2huMTgybzJ1dFktUjJWZlMyak14S0tEUTNBdHB5d1J3eDduTVRsVm1QaWN5c1N6WnR4TFJQUF9SUGF0WUV0VUtsTHoySTRGQk9IaXVDc0s0STh0UzVZbndvMmN3bDhXaEFTd3gwNjBNdjM3cDJLMjV3YUlqT1preDRDUVlPcjlKUGpxazZSaWsydEpIQmZUMGgwX2ZOR2dQQjlEbkVqLW1WUzhVV2F3R0MxbERJeGhZTGVib3M3TGFySnNaLVNlWG5BREU5aDFpbk1JRG11Q0s5Nzc3Qi1QdnlsOE5LRE9SOGZKYjVZdUFkN0ZuOUYzV1FOYkU2bzEwc0pvREtyZE84cnZnTWZiQzZMTGZlVGRiNmJkZGRrZzdBMnlvM1l5OXR5Vm1DZFpfRHdKMVd2RTlzTnRFX1h6R2NHRzZHaTlXbl9ydndpRUI0NERSejZfRTBTRkxQVHpxQWFyNGstb19KakNiTHk2eWpuQk1B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNM2Iwdm13dDY0dVFwcVlQMG5vYnNVY0ZKUzU1Y182YnpXckxwN0JSWmktbVAzWXd5d01UbktqWW5kWW16RGN5OGR1RENCbFkwQWZzNko1bVF6QlBHWVBJdnVlNUR0b0FxRmtzWlF3SWw2Q0hXQm5lV083RzB4ZXhHUWJySmhGZ3VDY2tzLW5KZTU1WmNxQ0FaQVBsdVJtN0ZEWldrczBHcm42R21Xemc?oc=5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4214,38 +4214,38 @@
         </is>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46113.78525462963</v>
+        <v>46113.855625</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>High Level City France French</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris" OR "Île-de-France") AND ("alerte à la bombe" OR "colis suspect" OR "menace à la bombe" OR fusillade OR "attentat" OR "attaque au couteau" OR "opération de police" OR évacuation) AND -immobilier AND -"prix immobilier" AND -foot AND -transfert AND -Texas</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Woman (63) charged with murder after Dublin house party stabbing ‘too unwell’ to attend hearing - Sunday World</t>
+          <t>Attentat déjoué contre Bank of America : quatre jeunes écroués à Paris - France 24</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Woman (63) charged with murder after Dublin house party stabbing ‘too unwell’ to attend hearing - Sunday World</t>
+          <t>Attack foiled against Bank of America: four young people imprisoned in Paris - France 24</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 16:48:00 GMT</t>
+          <t>Thu, 02 Apr 2026 06:22:48 GMT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxQOEU2dEVBcnVUbTVTMkRkR0pDeElOYzRIek1nM2dqRWpRd0FEeDJXaVZFci1LbVZndG1IUDJfcTlVelN6a2FfYXRKVy1RaWt0S1pLV3NvQ0RuTy01eUE0UDlQYmJzV0hJSHVBOWtsRnVydkxHTmF2eDZNVFBRdWl5V1JMTHROWExCVFZKVXkzNXV1azVNVWdfalpRM0VjWnd3d1RiRDBaWkZZUGQ4cVV3dVdEWDFhbjVQTTJoOGNrY3V4dVQ3YVI3X2NRT0xtNEVpR0NhM0ZvWXBKUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQaG5BU3QzN3JybmlRV2oxMGtBM1V2ZnVmMWhnRnRTWFJXdHo2T05Ia0UyZzhvRVBvVjBqUFpncUpqU1lfOWhzZnFNZHhjR2cwMDJxajlfcUFacnRjNzdPcHQtTm9uZ0N3R19IT2ZxcUVnZl9rU3VOSmxwRXlxMDAzZ2ZfNG1WUWlKUnNwN0ZWampzdHVNY0N5X3BKcDAwMER4T2QtLTBaWjZHb1dSOFNCanpOYVZWM0xHckRpdXMwZmVEV0JWUTB3RkdB?oc=5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4255,52 +4255,52 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>FR:fr</t>
         </is>
       </c>
       <c r="K70" s="1" t="n">
-        <v>46113.7</v>
+        <v>46114.26583333333</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>High Level City France French</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Paris" OR "Île-de-France") AND ("alerte à la bombe" OR "colis suspect" OR "menace à la bombe" OR fusillade OR "attentat" OR "attaque au couteau" OR "opération de police" OR évacuation) AND -immobilier AND -"prix immobilier" AND -foot AND -transfert AND -Texas</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Irish deputy premier describes proxy bomb attempt in Lurgan as ‘deeply chilling’ - london-now.co.uk</t>
+          <t>Attentat déjoué à Paris : Un jeune majeur suspecté d’avoir recruté trois ados et écroué - Yahoo Actualités</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Irish deputy premier describes proxy bomb attempt in Lurgan as ‘deeply chilling’ - london-now.co.uk</t>
+          <t>Attack foiled in Paris: A young adult suspected of having recruited three teenagers and imprisoned - Yahoo News</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 08:49:32 GMT</t>
+          <t>Wed, 01 Apr 2026 17:04:22 GMT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQdE13ckF0dFdZc3llalNyX0NUMUhNWGxwU1VBbTRfcjBRT3BMWTdvR2tRd21reERGVVk1YU93NWN6TTNwWjloSmpYc3lPenZFUUJBenpGcjhQYnZDTm5CemdnVnFFWFVCQk5XLWw2eGNTWjhhQkthcU9DVm5IbFo4YTZsb21lY1hSa3J0Q3RuNm1abUtCb2o1dW5FUkpQdldzVkhSaWllSS1HT1l4ZHVuVHpkUFZoYW5YYVhQNk1Ld0VXUlk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQUERUQTFDNk9XMG1YNHpsZWFXRkZpM1RGUEUwUG51MHlvQ1hfaUlPSmhDdHJRc3FaY3F5elctNFBodW5PNzIyR2lTWVVjWjFWTXQxT1Z5M2NWaGF3Wmx6TnRwTHBFWFd0TC11Vy1mMFRNNGlUejJ1OF9EWFdkSXFCQ3ZhSTRBa1EtOFdCRFJB?oc=5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4310,52 +4310,52 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>FR:fr</t>
         </is>
       </c>
       <c r="K71" s="1" t="n">
-        <v>46113.36773148148</v>
+        <v>46113.71136574074</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Village La Vallee</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("La Vallee Village" OR "LaValleeVillage" OR "LaValleeVillage" OR "Ingolstadt Village" OR "IngolstadtVillage" OR "IngolstadtVillage")</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tributes paid to 26-year-old Nahom Medhanie after fatal shooting in Camden | News - Greatest Hits Radio (London) - Rayo</t>
+          <t>Most Coveted: Our March Fashion &amp; Beauty Favorites - Coveteur</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tributes paid to 26-year-old Nahom Medhanie after fatal shooting in Camden | News - Greatest Hits Radio (London) - Rayo</t>
+          <t>Most Coveted: Our March Fashion &amp; Beauty Favorites - Coveteur</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 13:42:01 GMT</t>
+          <t>Wed, 01 Apr 2026 23:02:11 GMT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinwFBVV95cUxQTWRKX09FR3lTT3pqZ3pMT0NmbnluMDVCcGVqVDZvSW00UFRhalotUmhQajdfWlFWOF9GWURDdDJFZ1BHRXlQRXlNYWVXZGFoTXJLNmZjTVA0UndOckhxUEZkbnNqck5sQkhsTDlwdFZ4SWlCbWN3ekVxTmo3RVlYSG1LSHRnWURtNFRvMFF0QkVGTXJaTzh4Q1Uwb01wTUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE90OEpNX1p2MlFmWndxbUxmWXByYzh1OVU5SVBoSWNiYl84dllIenVJd2J6R04xblhROU5QSFZLOVlZYkxKOW5jSWVCeXRqT0tCbmxBX19KNkJoazA?oc=5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4379,38 +4379,38 @@
         </is>
       </c>
       <c r="K72" s="1" t="n">
-        <v>46113.57084490741</v>
+        <v>46113.95984953704</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" )</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hotel migrant faces jail after staging MI5 bomb hoax over failed asylum claim - gbnews.com</t>
+          <t>Sciopero dei trasporti aprile 2026: calendario e orari città per città - Virgilio</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Hotel migrant faces jail after staging MI5 bomb hoax over failed asylum claim - gbnews.com</t>
+          <t>Transport strike April 2026: calendar and timetables city by city - Virgilio</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 20:32:06 GMT</t>
+          <t>Thu, 02 Apr 2026 06:00:00 GMT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNM2Iwdm13dDY0dVFwcVlQMG5vYnNVY0ZKUzU1Y182YnpXckxwN0JSWmktbVAzWXd5d01UbktqWW5kWW16RGN5OGR1RENCbFkwQWZzNko1bVF6QlBHWVBJdnVlNUR0b0FxRmtzWlF3SWw2Q0hXQm5lV083RzB4ZXhHUWJySmhGZ3VDY2tzLW5KZTU1WmNxQ0FaQVBsdVJtN0ZEWldrczBHcm42R21Xemc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxORU5PTi0xQ2pNdkpYenBObHRvN0VILXdhOFg5UXg3cmNRWE1QNDFDaE1kYzZaLVRydEZaTjZXQnN6VDAxUmJQMU9xaWVJRWxoQ3FCaEV3Wk1uUDlGWjI1a0VpdzBlZ0ZKNFBjR05nYWRwMVdnTG01dGRjUDVmaUNyZ3VmMTVtQmpybDcxN3ROVGFYdXNiemdOM2xvLTRJXzJsZG1YM0Q5SWF5Zw?oc=5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4420,52 +4420,52 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K73" s="1" t="n">
-        <v>46113.855625</v>
+        <v>46114.25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>High Level City France French</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>("Paris" OR "Île-de-France") AND ("alerte à la bombe" OR "colis suspect" OR "menace à la bombe" OR fusillade OR "attentat" OR "attaque au couteau" OR "opération de police" OR évacuation) AND -immobilier AND -"prix immobilier" AND -foot AND -transfert AND -Texas</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Attentat déjoué contre la Bank of America à Paris : trois mineurs et un majeur, suspecté de les avoir recrutés, mis en examen - franceinfo.fr</t>
+          <t>Corteo Pro-Pal in centro a Bologna contro “la pena di morte per i partigiani palestinesi” - Il Resto del Carlino</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Foiled attack against the Bank of America in Paris: three minors and an adult, suspected of having recruited them, indicted - franceinfo.fr</t>
+          <t>Pro-Pal procession in the center of Bologna against "the death penalty for Palestinian partisans" - Il Resto del Carlino</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:42:29 GMT</t>
+          <t>Wed, 01 Apr 2026 21:12:42 GMT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8wJBVV95cUxNdWM2cEs0WEthQkJqS3pxeURUenkzM1F6cVJtYW52Q1QtWmN5MmpiNXF1QkZvdFk4bk1tMWRlS2NkSFBQWEE3RjdZMmxSelZlMzZTSl9Ia251ZnJRenhlZXpiNzZOX2dOTEpzcG5ZeUFVemszZTVZZnNoQ1lBY05YeFJad0NwSVBLbTBCOEE1dE00a2hMUzRsZXFRcjY4OHp4T0p0WHI0aHpYY3pQTGpuY3hleG9HdGVRbndHczQtSE5pSDQ5R09XWHBPMnRYODJrM2hCVUhKbHA5b010bnpXSU5RMWZweUFud3czdXFHczhxNEM5Z1hISXJGZWZFTjROcXc3TklCa1diemJIamlmZDJ5bVptQ0E3OEZsNFBMdC05Z09QTU9vakljdDExd2lCRDNpNVlReHc3OEljRGJnMnVJQWNidVpwLWhqcFAyVVRoNWtvSm05cDlDM29wWTk4SF9SNDM0ZExxbnI5Y295T2UzNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9xX29jNElSOUpCNGpDQTVTVDk0cmRscnNZM1pzb2JJcnZyY2U5VGtqVzdqTXE3b1lmcV9obm1mRHJXNnVmcEtpYVNwM2dERl9vQkVlWTZUSmw3RGJweTFWMjBBQ1R6dU5JZTV0WkZHYTZLOUZuVHdVb0VPcjA?oc=5</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4475,52 +4475,52 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>FR:fr</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K74" s="1" t="n">
-        <v>46113.73783564815</v>
+        <v>46113.88381944445</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>High Level City France French</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>("Paris" OR "Île-de-France") AND ("alerte à la bombe" OR "colis suspect" OR "menace à la bombe" OR fusillade OR "attentat" OR "attaque au couteau" OR "opération de police" OR évacuation) AND -immobilier AND -"prix immobilier" AND -foot AND -transfert AND -Texas</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Attentat contre la Bank of America déjoué à Paris : un homme d’une vingtaine d’années soupçonné d’avoir recruté trois adolescents - Le Monde.fr</t>
+          <t>La protesta al cimitero: "Tutelare diritti e stipendi" - Il Giorno</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Attack against the Bank of America foiled in Paris: a man in his twenties suspected of having recruited three teenagers - Le Monde.fr</t>
+          <t>The protest at the cemetery: "Protect rights and salaries" - Il Giorno</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 09:28:00 GMT</t>
+          <t>Thu, 02 Apr 2026 04:43:59 GMT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAJBVV95cUxQUHBxZUt4VHhLQlVUb1ZEcXNfU1czM1lwc0NONlJEZ3ItUGxWM1g5d2d1MUNWZ1IxNjhOT2xDX0hzQWltN3g1c21BVDlUbVRNZWZ6RTJDUThwSDd4MlVjS2p5SUZteVZNOHp1ZWQxeWlBWEdySHQ3WDl6M0FmOTU4RzJXeDZqY3RkQ0NsZ2QxYzdWUlBlZnFpNkkzV0N2WWRQMmFvNUdkSjh3c3V3cmp4dkpHWEFGRkpCZjZoTE05dGU3c043RGhaRTRBQnBVTW5JeEE1RFo0eUl4YV9yTS1KUDdYVTVKSzBURGMxaHcyOXVUZkNxSnNXcXVULVVnbEdiZWl0YkRWdjNDeWNza0pvM3Z2Yjk3Q3ozelo2b0wzbkU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNYjBzbTlPeGR3MVFDaGNjbXNCQjdFRXZWRTRPM0RFajRPaFF5SGZYNFo3ak5GdEhJTUV3MHhZVXlETlJ6U0ppckxRLVc2a3FkbTFOZ2FlVHJaSkpnZUVJMGJWd2UzNk8zNDNuTlgyd3E2ZkVhenI1bVhxblJxVldwaFhSMzFzd3E1OFZnRlh4LTI?oc=5</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4530,52 +4530,52 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>FR:fr</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46113.39444444444</v>
+        <v>46114.19721064815</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>High Level City France French</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>("Paris" OR "Île-de-France") AND ("alerte à la bombe" OR "colis suspect" OR "menace à la bombe" OR fusillade OR "attentat" OR "attaque au couteau" OR "opération de police" OR évacuation) AND -immobilier AND -"prix immobilier" AND -foot AND -transfert AND -Texas</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Attentat déjoué à Paris : Un jeune majeur suspecté d’avoir recruté trois ados et écroué - Yahoo Actualités</t>
+          <t>Mezza giornata di sciopero in Piazza Affari il 30 aprile - ANSA</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Attack foiled in Paris: A young adult suspected of having recruited three teenagers and imprisoned - Yahoo News</t>
+          <t>Half day of strike in Piazza Affari on 30 April - ANSA</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:04:22 GMT</t>
+          <t>Wed, 01 Apr 2026 17:11:44 GMT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQUERUQTFDNk9XMG1YNHpsZWFXRkZpM1RGUEUwUG51MHlvQ1hfaUlPSmhDdHJRc3FaY3F5elctNFBodW5PNzIyR2lTWVVjWjFWTXQxT1Z5M2NWaGF3Wmx6TnRwTHBFWFd0TC11Vy1mMFRNNGlUejJ1OF9EWFdkSXFCQ3ZhSTRBa1EtOFdCRFJB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQaUdTUjFkYmhjUlRzOVRjNWx2WnRQLWxMOWlWRVJUanhKYVh1ZHdqbUZqblZCZXdRNThxdWlWQ1JqdjVkdVllZ2picEdYQTdPUEg5VFBSeTZPSGJPVHNaX01XRW5kS1VBbzZLM1JEQlVjVUtyekhEcFdmVEg0M3Bzc0RUX25RSmdjN2VqeHVpNUtmNExDbzZXdWxpbEdVVkFZUmp6c0RwNGc1bzF4ay1jbURyenE0Y3Rhd1pNakJlZ0hrNU1KMmZRbUtvSmo3c0lvb3NMZzIwMmpyUkhBa2JFZlZYbi1jMmpacHhB0gHrAUFVX3lxTFBpR1NSMWRiaGNSVHM5VGM1bHZadFAtbEw5aVZFUlRqeEphWHVkd2ptRmpuVkJld1E1OHF1aVZDUmp2NWR1WWVnamJwR1hBN09QSDlUUFJ5Nk9IYk9Uc1pfTVdFbmRLVUFvNkszUkRCVWNVS3J6SERwV2ZUSDQzcHNzRFRfblFKZ2M3ZWp4dWk1S2Y0TENvNld1bGlsR1VWQVlSanpzRHA0ZzVvMXhrLWNtRHJ6cTRjdGF3Wk1qQmVnSGs1TUoyZlFtS29KajdzSW9vc0xnMjAyanJSSEFrYkVmVlhuLWMyalpweEE?oc=5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4585,52 +4585,52 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>FR:fr</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K76" s="1" t="n">
-        <v>46113.71136574074</v>
+        <v>46113.71648148148</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Village La Vallee</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>("La Vallee Village" OR "LaValleeVillage" OR "LaValleeVillage" OR "Ingolstadt Village" OR "IngolstadtVillage" OR "IngolstadtVillage")</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Most Coveted: Our March Fashion &amp; Beauty Favorites - Coveteur</t>
+          <t>Dl Sicurezza al rallenty. Parte l’ostruzionismo - ilmanifesto.it</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Most Coveted: Our March Fashion &amp; Beauty Favorites - Coveteur</t>
+          <t>DL Safety in slow motion. The obstructionism begins - ilmanifesto.it</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 23:02:11 GMT</t>
+          <t>Wed, 01 Apr 2026 22:15:43 GMT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE90OEpNX1p2MlFmWndxbUxmWXByYzh1OVU5SVBoSWNiYl84dllIenVJd2J6R04xblhROU5QSFZLOVlZYkxKOW5jSWVCeXRqT0tCbmxBX19KNkJoazA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBER2dYaWhXb1lqOXpIaE5nRnduT0F0SkU1MXJPc1ROLXU5N01lbE9YQ0xRdDVIbTd3LU0tT0ZQdHlzcjhySURpT3VldU5BUXk1S0RUakVja0IwTWVwTDZmaXJ4SkRPNTVkLTlFUDR1SzRwdkFKRnpF?oc=5</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4640,21 +4640,21 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K77" s="1" t="n">
-        <v>46113.95984953704</v>
+        <v>46113.92758101852</v>
       </c>
     </row>
     <row r="78">
@@ -4670,22 +4670,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sciopero dei trasporti aprile 2026: calendario e orari città per città - Virgilio</t>
+          <t>MILANO: LA PROCURA IPOTIZZA TURBATIVA D’ASTA E RIVELAZIONE SEGRETI D’UFFICIO PER LA VENDITA DI SAN SIRO - Radio Onda d`Urto</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Transport strike April 2026: calendar and timetables city by city - Virgilio</t>
+          <t>MILAN: THE PROSECUTOR'S PROSECUTION HIGHLIGHTS AUCTION RIGGING AND REVELATION OF OFFICE SECRETS FOR THE SALE OF SAN SIRO - Radio Onda d`Urto</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 06:00:00 GMT</t>
+          <t>Wed, 01 Apr 2026 18:02:00 GMT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxORU5PTi0xQ2pNdkpYenBObHRvN0VILXdhOFg5UXg3cmNRWE1QNDFDaE1kYzZaLVRydEZaTjZXQnN6VDAxUmJQMU9xaWVJRWxoQ3FCaEV3Wk1uUDlGWjI1a0VpdzBlZ0ZKNFBjR05nYWRwMVdnTG01dGRjUDVmaUNyZ3VmMTVtQmpybDcxN3ROVGFYdXNiemdOM2xvLTRJXzJsZG1YM0Q5SWF5Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPMlJhZmxIT2lfOVdwMTNCdXpHcUIzSDZpcG9HWEI3UzRydDZzOEtGV2FxWFBoNF9vMjRnSkhBb2xyWERLRUo5NDJEMVc0QW5Wd1Bma080VGZNbEJWMjQ4dFpkN2I1TzFlX3pRQS1KV2dLNmpUZnFuM3dldEhROWVNdWkwUll3SjVRX0Z5QnpuQ2w1M2lQZGlYcVpYYXRHUGdDWmNuWnh3TVNXVWF6eVVyYzR4NFNyUnR5Qzg2cGdMSjg0QVU5d1JqakpLc2JycWRQOHF1T1hyclREdw?oc=5</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="K78" s="1" t="n">
-        <v>46114.25</v>
+        <v>46113.75138888889</v>
       </c>
     </row>
     <row r="79">
@@ -4725,22 +4725,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Corteo Pro-Pal in centro a Bologna contro “la pena di morte per i partigiani palestinesi” - Il Resto del Carlino</t>
+          <t>Lombardia. Opposizioni, sindacati e cittadini promuovono manifestazione per il diritto alla salute - Quotidiano Sanità</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Pro-Pal procession in the center of Bologna against "the death penalty for Palestinian partisans" - Il Resto del Carlino</t>
+          <t>Lombardy. Oppositions, unions and citizens promote demonstration for the right to health - Quotidiano Sanità</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 21:12:42 GMT</t>
+          <t>Wed, 01 Apr 2026 12:39:36 GMT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE9xX29jNElSOUpCNGpDQTVTVDk0cmRscnNZM1pzb2JJcnZyY2U5VGtqVzdqTXE3b1lmcV9obm1mRHJXNnVmcEtpYVNwM2dERl9vQkVlWTZUSmw3RGJweTFWMjBBQ1R6dU5JZTV0WkZHYTZLOUZuVHdVb0VPcjA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNZngxRWMzLXkzTFhMZWdRcTIycTFLZUlmMTRRNGlHWExyc3IzM08tdFg4LU83bHgxN1ZQZThkWVV2U0FhLTV0MlhlemlocTdwRXh4SGZwOGxQVms5Rzd2aWtISVhwUHFWak1kcm9OUWZ3ZEh5RHdIOUlaTzJmOHBjNXRPUDNHRGRTWGo4RWNOcTRTRk9XOHNvYUN6S0hKMG5NbXJMVXVRNW5DWXlTdVhzemloYVd3ZmcwR0pMdnpOM3dIVGxVaWdIc2NneGppT1NjVVNjRVd3?oc=5</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="K79" s="1" t="n">
-        <v>46113.88381944445</v>
+        <v>46113.5275</v>
       </c>
     </row>
     <row r="80">
@@ -4780,22 +4780,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mezza giornata di sciopero in Piazza Affari il 30 aprile - ANSA</t>
+          <t>Puglia isolata: fiumi in piena e ferrovie bloccate, impossibile raggiungere Roma e Milano - Quotidiano Di Puglia</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Half day of strike in Piazza Affari on 30 April - ANSA</t>
+          <t>Puglia isolated: rivers in flood and railways blocked, impossible to reach Rome and Milan - Quotidiano Di Puglia</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 17:11:44 GMT</t>
+          <t>Wed, 01 Apr 2026 18:10:41 GMT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxQaUdTUjFkYmhjUlRzOVRjNWx2WnRQLWxMOWlWRVJUanhKYVh1ZHdqbUZqblZCZXdRNThxdWlWQ1JqdjVkdVllZ2picEdYQTdPUEg5VFBSeTZPSGJPVHNaX01XRW5kS1VBbzZLM1JEQlVjVUtyekhEcFdmVEg0M3Bzc0RUX25RSmdjN2VqeHVpNUtmNExDbzZXdWxpbEdVVkFZUmp6c0RwNGc1bzF4ay1jbURyenE0Y3Rhd1pNakJlZ0hrNU1KMmZRbUtvSmo3c0lvb3NMZzIwMmpyUkhBa2JFZlZYbi1jMmpacHhB0gHrAUFVX3lxTFBpR1NSMWRiaGNSVHM5VGM1bHZadFAtbEw5aVZFUlRqeEphWHVkd2ptRmpuVkJld1E1OHF1aVZDUmp2NWR1WWVnamJwR1hBN09QSDlUUFJ5Nk9IYk9Uc1pfTVdFbmRLVUFvNkszUkRCVWNVS3J6SERwV2ZUSDQzcHNzRFRfblFKZ2M3ZWp4dWk1S2Y0TENvNld1bGlsR1VWQVlSanpzRHA0ZzVvMXhrLWNtRHJ6cTRjdGF3Wk1qQmVnSGs1TUoyZlFtS29KajdzSW9vc0xnMjAyanJSSEFrYkVmVlhuLWMyalpweEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwFBVV95cUxOSmhvTW1TVS1KRTd1eHZUR2h5WkFHUTU3TE5VZWswa2dEdk5YOURMbDhSaFhlcGgwZW5JVHRZTnp4ZGExZ2VZVFVwRTFmSExvT1dfZXhhalROTXA3OXhKVHgzOUJ3S0pJLXhIR3pzM2xRLUpMY3ZEWVFlSWF1dDEySFlpckNPTWprTUtPTXRoY3ZCZXRtNHhHWFEtYVVtZlBETmJINXZXSVY1aFBwbGk00gG0AUFVX3lxTE1ia0t6LUpxNFB6UHozSE5YbGlDYkdIOUJaSjJxSWlFaTlWZW5teDVvLWp4N3JiUG01dU0xV3N6SHRLdnYzWkNmSXM5aXF2bUNWYmlxYkRhVjVLUTkwVlA3NmdVT0FkcTlEVjdOeHNmSkR1V2FsTFc3QmNPazJucmVXV084WElZX2s2MlJNOGI3akh0NFlFY0tvYzNOWUNKSTdZOEhLM1JuRXFxUVNwempUSDd2bA?oc=5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4819,7 +4819,7 @@
         </is>
       </c>
       <c r="K80" s="1" t="n">
-        <v>46113.71648148148</v>
+        <v>46113.75741898148</v>
       </c>
     </row>
     <row r="81">
@@ -4835,22 +4835,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>La protesta al cimitero: "Tutelare diritti e stipendi" - Il Giorno</t>
+          <t>Bloccata la linea Caserta-Foggia, caos treni a Bari: ritardi e corse cancellate - BariToday</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>The protest at the cemetery: "Protect rights and salaries" - Il Giorno</t>
+          <t>The Caserta-Foggia line blocked, train chaos in Bari: delays and canceled journeys - BariToday</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 04:43:59 GMT</t>
+          <t>Wed, 01 Apr 2026 16:07:00 GMT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNYjBzbTlPeGR3MVFDaGNjbXNCQjdFRXZWRTRPM0RFajRPaFF5SGZYNFo3ak5GdEhJTUV3MHhZVXlETlJ6U0ppckxRLVc2a3FkbTFOZ2FlVHJaSkpnZUVJMGJWd2UzNk8zNDNuTlgyd3E2ZkVhenI1bVhxblJxVldwaFhSMzFzd3E1OFZnRlh4LTI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxORzVmaWt0MmxDaHFFVGVQZzF1Ym12U1FCNUxZMWNkdHpVVXNOWmJBU1ExWEgtVTdIdENYVm5pYjJ2UzJueHJyNUVxV2xOazBTYmNVQ2Zib3ZIWEtuSktTQUowQ2UwOGh4RUFRZDJzVXd4QS1wcjlZbDJ5ZnpyVHFHdW9uVVdQTzdPaXpXeDU2dTM?oc=5</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="K81" s="1" t="n">
-        <v>46114.19721064815</v>
+        <v>46113.67152777778</v>
       </c>
     </row>
     <row r="82">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MILANO: APERTO IL PROCESSO CIVILE CONTRO LE MAMME ANTIFASCISTE DEL LEONCAVALLO. IL VIMINALE CHIEDE OLTRE 3 MILIONI DI EURO - Radio Onda d`Urto</t>
+          <t>​Autopromotec e BolognaFiere rinnovano l’accordo fino al 2033 - Notiziario Motoristico</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>MILAN: THE CIVIL TRIAL AGAINST THE ANTI-FASCIST MOMS OF LEONCAVALLO OPENED. THE VIMINAL ASKS FOR OVER 3 MILLION EUROS - Radio Onda d`Urto</t>
+          <t>​Autopromotec and BolognaFiere renew the agreement until 2033 - Motoring News</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 11:48:00 GMT</t>
+          <t>Thu, 02 Apr 2026 08:09:42 GMT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOd0FIT3B5YWVlSHRndU1IcWs1ODJkXzIzejFTckEwVnRzeXdvcm1CYy1NNkFXdkpkcGxaMUZFdTlkal95ekd3b3ozdWZnREt6R095bi15TUNrU1RQNThELUYzTXh4TjFqNmR6X19IZDdzMDdIUzFBWE1Sbk82ajlkYjdDSlZMc0EzNDlJSGJhVkNweEN5VFc1TmRtazN2MmZIQUdQRy1SZ2dHSXMxMk5HdEdyY1Nuc29jWFkzUHcyMVpJN1JBYUNMaml5OWVVT2lBallEeEFLLTBwS1FwY3RZWmNBeExfRTdnYWlpVnk5NE9JNTBm?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxNdHFyV0FYUHlueVBsQ3V0c2VXMWVXMVlZeEhGWTFpR2I5WlRBSmNSU2haNkRZZXJiVTRibTRDQkRRb3hrQlRNYVZheGY3U3hBZm1ULUItazlaN3dvb1gxTG9pMDF2a1lyNzZXUVllNklGWHhsaHpGUDhyZnYzemVydlpobTBuV2p2Z2ZrUi1PczFfNzZaMzVtREZ3TDIxRkZwcnk4STJHRG1PSnpk?oc=5</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="K82" s="1" t="n">
-        <v>46113.49166666667</v>
+        <v>46114.34006944444</v>
       </c>
     </row>
     <row r="83">
@@ -4945,22 +4945,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lombardia. Opposizioni, sindacati e cittadini promuovono manifestazione per il diritto alla salute - quotidianosanita.it</t>
+          <t>MILANO: APERTO IL PROCESSO CIVILE CONTRO LE MAMME ANTIFASCISTE DEL LEONCAVALLO. IL VIMINALE CHIEDE OLTRE 3 MILIONI DI EURO - Radio Onda d`Urto</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Lombardy. Oppositions, unions and citizens promote demonstration for the right to health - ufficiosanita.it</t>
+          <t>MILAN: THE CIVIL TRIAL AGAINST THE ANTI-FASCIST MOMS OF LEONCAVALLO OPENED. THE VIMINAL ASKS FOR OVER 3 MILLION EUROS - Radio Onda d`Urto</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 12:39:36 GMT</t>
+          <t>Wed, 01 Apr 2026 11:48:00 GMT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxNZngxRWMzLXkzTFhMZWdRcTIycTFLZUlmMTRRNGlHWExyc3IzM08tdFg4LU83bHgxN1ZQZThkWVV2U0FhLTV0MlhlemlocTdwRXh4SGZwOGxQVms5Rzd2aWtISVhwUHFWak1kcm9OUWZ3ZEh5RHdIOUlaTzJmOHBjNXRPUDNHRGRTWGo4RWNOcTRTRk9XOHNvYUN6S0hKMG5NbXJMVXVRNW5DWXlTdVhzemloYVd3ZmcwR0pMdnpOM3dIVGxVaWdIc2NneGppT1NjVVNjRVd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOd0FIT3B5YWVlSHRndU1IcWs1ODJkXzIzejFTckEwVnRzeXdvcm1CYy1NNkFXdkpkcGxaMUZFdTlkal95ekd3b3ozdWZnREt6R095bi15TUNrU1RQNThELUYzTXh4TjFqNmR6X19IZDdzMDdIUzFBWE1Sbk82ajlkYjdDSlZMc0EzNDlJSGJhVkNweEN5VFc1TmRtazN2MmZIQUdQRy1SZ2dHSXMxMk5HdEdyY1Nuc29jWFkzUHcyMVpJN1JBYUNMaml5OWVVT2lBallEeEFLLTBwS1FwY3RZWmNBeExfRTdnYWlpVnk5NE9JNTBm?oc=5</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="K83" s="1" t="n">
-        <v>46113.5275</v>
+        <v>46113.49166666667</v>
       </c>
     </row>
     <row r="84">
@@ -5000,22 +5000,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bloccata la linea Caserta-Foggia, caos treni a Bari: ritardi e corse cancellate - BariToday</t>
+          <t>Quattromila ragazzi di Cl in corteo per la via crucis - Il Resto del Carlino</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>The Caserta-Foggia line blocked, train chaos in Bari: delays and canceled journeys - BariToday</t>
+          <t>Four thousand CL kids in procession along the Via Crucis - Il Resto del Carlino</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 16:07:00 GMT</t>
+          <t>Thu, 02 Apr 2026 03:31:37 GMT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxORzVmaWt0MmxDaHFFVGVQZzF1Ym12U1FCNUxZMWNkdHpVVXNOWmJBU1ExWEgtVTdIdENYVm5pYjJ2UzJueHJyNUVxV2xOazBTYmNVQ2Zib3ZIWEtuSktTQUowQ2UwOGh4RUFRZDJzVXd4QS1wcjlZbDJ5ZnpyVHFHdW9uVVdQTzdPaXpXeDU2dTM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPUWVTbEowNk5aSHhyTmxhazBGMV9hMGlMZlI2cmRzdGJWY2tBRUZKTXk1dUtxTUQtM2o2NXZFaVo0VVNvU2JkZ20wY1E4a2RIaWFkZ0M2aHFCMk5lTDdvVy1UYkFjZEJ3MG9hMFVEa1J0U1dZU1A5cUdXTkt2R0NBeTlFQ3cxUkNrUVUydWtn?oc=5</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -5039,7 +5039,7 @@
         </is>
       </c>
       <c r="K84" s="1" t="n">
-        <v>46113.67152777778</v>
+        <v>46114.14695601852</v>
       </c>
     </row>
     <row r="85">
@@ -5055,22 +5055,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dl Sicurezza al rallenty. Parte l’ostruzionismo - il manifesto</t>
+          <t>Pavoni, il confronto in Regione. La proprietà conferma il ’trasloco’ - Il Giorno</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DL Safety in slow motion. The obstructionism begins - the manifesto</t>
+          <t>Pavoni, the comparison in the Region. The ownership confirms the 'move' - Il Giorno</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 22:15:43 GMT</t>
+          <t>Thu, 02 Apr 2026 03:45:12 GMT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTFBER2dYaWhXb1lqOXpIaE5nRnduT0F0SkU1MXJPc1ROLXU5N01lbE9YQ0xRdDVIbTd3LU0tT0ZQdHlzcjhySURpT3VldU5BUXk1S0RUakVja0IwTWVwTDZmaXJ4SkRPNTVkLTlFUDR1SzRwdkFKRnpF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNQUYwbkNUdDUtcW9HNnN5aWhCVXlpbGU5b21EOGh1b1phaF9RMHlBNGwzbE9hSDY5VmNfSDNHS2s3T3AweFBseVJndEYxRmpsRkJUOEhPT2loNWxkQy1ORTNqYUVfN3hhZ3ZyZFp2Wno2T19iYUxCY3pJQS14dk1aZkZ2SXI?oc=5</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5094,7 +5094,7 @@
         </is>
       </c>
       <c r="K85" s="1" t="n">
-        <v>46113.92758101852</v>
+        <v>46114.15638888889</v>
       </c>
     </row>
     <row r="86">
@@ -5110,22 +5110,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MILANO: LA PROCURA IPOTIZZA TURBATIVA D’ASTA E RIVELAZIONE SEGRETI D’UFFICIO PER LA VENDITA DI SAN SIRO - Radio Onda d`Urto</t>
+          <t>Scritte contro la Meloni. Il cartellone è spuntato davanti al circolo Stranieri - Il Resto del Carlino</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>MILAN: THE PROSECUTOR'S PROSECUTION HIGHLIGHTS AUCTION RIGGING AND REVELATION OF OFFICE SECRETS FOR THE SALE OF SAN SIRO - Radio Onda d`Urto</t>
+          <t>Writings against Meloni. The billboard appeared in front of the Stranieri - Il Resto del Carlino club</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 18:02:00 GMT</t>
+          <t>Thu, 02 Apr 2026 04:21:36 GMT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxPMlJhZmxIT2lfOVdwMTNCdXpHcUIzSDZpcG9HWEI3UzRydDZzOEtGV2FxWFBoNF9vMjRnSkhBb2xyWERLRUo5NDJEMVc0QW5Wd1Bma080VGZNbEJWMjQ4dFpkN2I1TzFlX3pRQS1KV2dLNmpUZnFuM3dldEhROWVNdWkwUll3SjVRX0Z5QnpuQ2w1M2lQZGlYcVpYYXRHUGdDWmNuWnh3TVNXVWF6eVVyYzR4NFNyUnR5Qzg2cGdMSjg0QVU5d1JqakpLc2JycWRQOHF1T1hyclREdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPM0pnM1ZkRTNGcktQU1YzaWRlVF93dFlzZk1RTDk3RzFwYkZFOFZKWDB3NzBQNWZQQTZIR1FneV9ZRFQtM0FxZFMwNkJLN2p1U1otTTFSOXJwLXBrbFNiWTdYTEdCdGlacVJJNmd3MnlmeHhLYTZILS11a2RBMUhkY2ViNEl1V3RCdU5PeV9JTV9OV0tNRFE?oc=5</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="K86" s="1" t="n">
-        <v>46113.75138888889</v>
+        <v>46114.18166666666</v>
       </c>
     </row>
     <row r="87">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Quattromila ragazzi di Cl in corteo per la via crucis - Il Resto del Carlino</t>
+          <t>Pd all’attacco sul Cup unico: “Ritardo colpa dei privati. La Regione dia un aut aut”. Il Welfare: no, collaborano - Il Giorno</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Four thousand CL kids in procession along the Via Crucis - Il Resto del Carlino</t>
+          <t>Pd attacks on the single Cup: "Delay is the fault of private individuals. The Region should give an either/or." Welfare: no, they collaborate - Il Giorno</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 03:31:37 GMT</t>
+          <t>Thu, 02 Apr 2026 00:03:27 GMT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPUWVTbEowNk5aSHhyTmxhazBGMV9hMGlMZlI2cmRzdGJWY2tBRUZKTXk1dUtxTUQtM2o2NXZFaVo0VVNvU2JkZ20wY1E4a2RIaWFkZ0M2aHFCMk5lTDdvVy1UYkFjZEJ3MG9hMFVEa1J0U1dZU1A5cUdXTkt2R0NBeTlFQ3cxUkNrUVUydWtn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTFA3bmt0eVJ5bnBzVkRZZUZETzV4LWdwUWhYSXl2ZWN0d2ZxN1M2QkdhcldqemdSVDRvX3FKS2MwMW10U2VlZFVlYXBHelljdjREQ3Z5UHgxWFk1NG1pZ0dJalIyNFB5YzV4cEcwZ2xHNUtOZw?oc=5</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="K87" s="1" t="n">
-        <v>46114.14695601852</v>
+        <v>46114.00239583333</v>
       </c>
     </row>
     <row r="88">
@@ -5220,22 +5220,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Perché Nordio ha deciso di mandare gli ispettori presso il tribunale di Bologna - BolognaToday</t>
+          <t>Mirandola celebra la Festa di Primavera 2026: domenica 19 aprile il grande corteo del principato di Francia Corta - Bologna 2000</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Why Nordio decided to send inspectors to the Bologna court - BolognaToday</t>
+          <t>Mirandola celebrates the Spring Festival 2026: on Sunday 19 April the great procession of the principality of Francia Corta - Bologna 2000</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wed, 01 Apr 2026 07:37:50 GMT</t>
+          <t>Thu, 02 Apr 2026 07:52:02 GMT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPMmh2TFd5NkN3M3ZTVDQyMXZaeWVlYVgzMDBjeEstYkdubGg2dFNwNGNfV2xMR0RZcXdWQkR1WnZ1MUg5M2dCOXp3SUltc0t4NklwY0g3UEMxaE1aaUlTMXRvMnVPaWhCYUNqZTdHYmlJcm85LUVoVVQybERQNUdubjRNal95aHlqZE5DQTM3aEJ1QXJ6aXU4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPenE0emRwTnVfdkFSX2RhNm81MFZ3VTFETmg2SEJza0V2aDF2Z21LQ3BtTlBaTk9TQ05VdEtxbE5HQnVDSVVQYVF2NTNvNzdwOHhiajFFa3NhUTVGLXJpeEszYVYyR2Y2ZXlZbzFKbXhqekJ1cktCdVpBM0dQUnJZRU4xaGx5anpxMDZvaDBNT1BQQVMybmdZWmk1aGk3YngwRkVrM0w4UVhva3lvV2ZvbDlpV0gwbGlkSTdyX09DVHZvbjFHX1hyR0RjNU1KSkpZUDIwUHlzeVB5c1R4VWdhdkxITWw4aTg?oc=5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="K88" s="1" t="n">
-        <v>46113.31793981481</v>
+        <v>46114.32780092592</v>
       </c>
     </row>
     <row r="89">
@@ -5275,22 +5275,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pavoni, il confronto in Regione. La proprietà conferma il ’trasloco’ - Il Giorno</t>
+          <t>Il traffico sulle autostrade oggi in tempo reale - Virgilio</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Pavoni, the comparison in the Region. The ownership confirms the 'move' - Il Giorno</t>
+          <t>Traffic on highways today in real time - Virgilio</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Thu, 02 Apr 2026 03:45:00 GMT</t>
+          <t>Thu, 02 Apr 2026 01:08:00 GMT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNQUYwbkNUdDUtcW9HNnN5aWhCVXlpbGU5b21EOGh1b1phaF9RMHlBNGwzbE9hSDY5VmNfSDNHS2s3T3AweFBseVJndEYxRmpsRkJUOEhPT2loNWxkQy1ORTNqYUVfN3hhZ3ZyZFp2Wno2T19iYUxCY3pJQS14dk1aZkZ2SXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNZWJTN2pGX0tzdHM4SVFoN1VONWFkN1hmaTg1YXY4eExYWlBOWmhXVDktbV9EaW9ycXlyUjBIRzIwWHVDQTZrVHVIRXJBMEdOejZ1UklpSEZyTzc5SEpWLVdRazlSZmxPVzQxZFZVTWpBUkhoZmJfVnJaVFhCZ1pXQmFIOF95MzYyb1BR?oc=5</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5314,7 +5314,7 @@
         </is>
       </c>
       <c r="K89" s="1" t="n">
-        <v>46114.15625</v>
+        <v>46114.04722222222</v>
       </c>
     </row>
     <row r="90">
@@ -5370,116 +5370,6 @@
       </c>
       <c r="K90" s="1" t="n">
         <v>46113.51180555556</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Il traffico sulle autostrade oggi in tempo reale - Virgilio</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Traffic on highways today in real time - Virgilio</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Thu, 02 Apr 2026 01:08:00 GMT</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNZWJTN2pGX0tzdHM4SVFoN1VONWFkN1hmaTg1YXY4eExYWlBOWmhXVDktbV9EaW9ycXlyUjBIRzIwWHVDQTZrVHVIRXJBMEdOejZ1UklpSEZyTzc5SEpWLVdRazlSZmxPVzQxZFZVTWpBUkhoZmJfVnJaVFhCZ1pXQmFIOF95MzYyb1BR?oc=5</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K91" s="1" t="n">
-        <v>46114.04722222222</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>High Level City Italy Italian</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Dall'Aquila al Ministero del Lavoro, sit in di protesta dei lavoratori Telecontact Center del gruppo TIM - AbruzzoLive</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>From L'Aquila to the Ministry of Labour, sit in protests by Telecontact Center workers of the TIM group - AbruzzoLive</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Wed, 01 Apr 2026 08:48:30 GMT</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOV3VZMlJjM3YxSklmMWFHSHRYTERVNG9rS2RYSV9XUEF6ajBvVnBHU0RsVnpCcXZkRWRXRWIwMVB3QXVrSGwzVmxRQ2tlTGN5eTFIRXZuQzdjT0c4UE9YRV9VMTZGWHdrb2FFU1lhcnJoak9wLWlQS0NDaG4zOGdaQ01GaFF3Q29CSmNvXzJJUFp6TlgwTk5wZTdsV2FHdUxhTnNTT1FMU0F1NUpESC1xcTlnZm9PekVqV0l5VG50VTZhQy1T?oc=5</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K92" s="1" t="n">
-        <v>46113.36701388889</v>
       </c>
     </row>
   </sheetData>
